--- a/Tests/BLE link testing/SentReceivedData.xlsx
+++ b/Tests/BLE link testing/SentReceivedData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BenMi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BenMi\Desktop\Tests\BLE link testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310CCB54-BC4E-4B40-A342-F39CF5174DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35717538-5131-4DA1-A4B6-85FB3442C35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{933AE846-AE8C-41A9-985C-90DAE8B16888}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sent values" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Sent values'!$W$10:$W$98</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +36,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -47,8 +50,30 @@
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="200">
   <si>
     <t>Adafruit FeatherSense</t>
   </si>
@@ -627,6 +652,27 @@
   </si>
   <si>
     <t>90(samples)/5340.15 seconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jitter </t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max </t>
+  </si>
+  <si>
+    <t>Std. Dev</t>
+  </si>
+  <si>
+    <t>Interarrival times</t>
+  </si>
+  <si>
+    <t>Check Match</t>
   </si>
 </sst>
 </file>
@@ -656,7 +702,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,6 +712,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,12 +749,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -716,11 +764,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -811,7 +867,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2091,7 +2147,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IE"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2213,7 +2269,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IE"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3767,7 +3823,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IE"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3934,7 +3990,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5354,7 +5410,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IE"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5521,7 +5577,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6957,7 +7013,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-IE"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7095,6 +7151,140 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Interarrival times</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Interarrival times</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+      <cx:extLst>
+        <cx:ext uri="ext:featex">
+          <cx:featureExtension feature="mp" drop="onModelChange">
+            <cx:offset top="0.053418636322021484"/>
+          </cx:featureExtension>
+        </cx:ext>
+      </cx:extLst>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000003-B784-4143-BA48-1B189DFDEE27}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r">
+              <cx:binCount val="100"/>
+            </cx:binning>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Inter-arrival times (s)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Inter-arrival times (s)</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+          <cx:extLst>
+            <cx:ext uri="ext:featex">
+              <cx:featureExtension feature="mp" drop="onModelChange">
+                <cx:offset top="-0.21367563307285309" left="-0.16025590896606445"/>
+              </cx:featureExtension>
+            </cx:ext>
+          </cx:extLst>
+        </cx:title>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Count</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+                </a:rPr>
+                <a:t>Count</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:numFmt formatCode="General" sourceLinked="0"/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7216,6 +7406,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9319,6 +9549,514 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -9463,6 +10201,84 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>186836</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>148735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>85481</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>85480</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C660282-C59C-B0AE-7DAF-5E6C0ACBE85F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="19427336" y="7768735"/>
+              <a:ext cx="7823445" cy="3937245"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IE" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9785,3643 +10601,4301 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AC98FB-A3BF-4FD7-BFA6-D2374D521CE7}">
-  <dimension ref="F2:AG100"/>
+  <dimension ref="G7:AG100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
     <col min="15" max="15" width="24.85546875" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="23" max="23" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F2" s="2"/>
+    <row r="7" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="J7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="Q7" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
     </row>
-    <row r="3" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F3" s="2"/>
+    <row r="8" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G8" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="4" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F4" s="2"/>
+    <row r="9" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G9" s="2" t="b" cm="1">
+        <f t="array" ref="G9">AND(K9:N9=S9:V9)</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2280</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>723</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T9" s="3">
+        <v>2280</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>723</v>
+      </c>
+      <c r="W9" s="1">
+        <f>(DATEVALUE(LEFT(Q9,10))+TIMEVALUE(MID(Q9,12,12)) - (DATEVALUE(LEFT(Q9,10))+TIMEVALUE(MID(Q9,12,12)))) * 86400</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F5" s="2"/>
+    <row r="10" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="b" cm="1">
+        <f t="array" ref="G10">AND(K10:N10=S10:V10)</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2250</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>766</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1</v>
+      </c>
+      <c r="S10" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2250</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>766</v>
+      </c>
+      <c r="W10" s="1">
+        <f>(DATEVALUE(LEFT(Q10,10))+TIMEVALUE(MID(Q10,12,12)) - (DATEVALUE(LEFT(Q9,10))+TIMEVALUE(MID(Q9,12,12)))) * 86400</f>
+        <v>60.000999737530947</v>
+      </c>
     </row>
-    <row r="6" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F6" s="2"/>
+    <row r="11" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G11" s="2" t="b" cm="1">
+        <f t="array" ref="G11">AND(K11:N11=S11:V11)</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L11" s="3">
+        <v>2244</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>815</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="R11" s="3">
+        <v>2</v>
+      </c>
+      <c r="S11" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T11" s="3">
+        <v>2244</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>815</v>
+      </c>
+      <c r="W11" s="1">
+        <f>(DATEVALUE(LEFT(Q11,10))+TIMEVALUE(MID(Q11,12,12)) - (DATEVALUE(LEFT(Q10,10))+TIMEVALUE(MID(Q10,12,12)))) * 86400</f>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="7" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F7" s="2"/>
-      <c r="J7" s="8" t="s">
+    <row r="12" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G12" s="2" t="b" cm="1">
+        <f t="array" ref="G12">AND(K12:N12=S12:V12)</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2279</v>
+      </c>
+      <c r="M12" s="3">
         <v>0</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="Q7" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
+      <c r="N12" s="3">
+        <v>844</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T12" s="3">
+        <v>2279</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>844</v>
+      </c>
+      <c r="W12" s="1">
+        <f>(DATEVALUE(LEFT(Q12,10))+TIMEVALUE(MID(Q12,12,12)) - (DATEVALUE(LEFT(Q11,10))+TIMEVALUE(MID(Q11,12,12)))) * 86400</f>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="8" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F8" s="2"/>
-      <c r="J8" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>95</v>
+    <row r="13" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G13" s="2" t="b" cm="1">
+        <f t="array" ref="G13">AND(K13:N13=S13:V13)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>4</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L13" s="3">
+        <v>2310</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>844</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="R13" s="3">
+        <v>4</v>
+      </c>
+      <c r="S13" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T13" s="3">
+        <v>2310</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>844</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" ref="W13:W74" si="0">(DATEVALUE(LEFT(Q13,10))+TIMEVALUE(MID(Q13,12,12)) - (DATEVALUE(LEFT(Q12,10))+TIMEVALUE(MID(Q12,12,12)))) * 86400</f>
+        <v>59.999999566935003</v>
       </c>
     </row>
-    <row r="9" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F9" s="2"/>
-      <c r="J9" s="5">
+    <row r="14" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="b" cm="1">
+        <f t="array" ref="G14">AND(K14:N14=S14:V14)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2254</v>
+      </c>
+      <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="5">
+      <c r="N14" s="3">
+        <v>820</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R14" s="3">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>2050</v>
       </c>
-      <c r="L9" s="5">
-        <v>2280</v>
-      </c>
-      <c r="M9" s="5">
+      <c r="T14" s="3">
+        <v>2254</v>
+      </c>
+      <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="5">
+      <c r="V14" s="3">
+        <v>820</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="15" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G15" s="2" t="b" cm="1">
+        <f t="array" ref="G15">AND(K15:N15=S15:V15)</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L15" s="3">
+        <v>2244</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>794</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" s="3">
+        <v>6</v>
+      </c>
+      <c r="S15" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T15" s="3">
+        <v>2244</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>794</v>
+      </c>
+      <c r="W15" s="1">
+        <f>(DATEVALUE(LEFT(Q15,10))+TIMEVALUE(MID(Q15,12,12)) - (DATEVALUE(LEFT(Q14,10))+TIMEVALUE(MID(Q14,12,12)))) * 86400</f>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="16" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="b" cm="1">
+        <f t="array" ref="G16">AND(K16:N16=S16:V16)</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
+        <v>7</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L16" s="3">
+        <v>2229</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>762</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R16" s="3">
+        <v>7</v>
+      </c>
+      <c r="S16" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T16" s="3">
+        <v>2229</v>
+      </c>
+      <c r="U16" s="3">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3">
+        <v>762</v>
+      </c>
+      <c r="W16" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="17" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G17" s="2" t="b" cm="1">
+        <f t="array" ref="G17">AND(K17:N17=S17:V17)</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L17" s="3">
+        <v>2229</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>764</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" s="3">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T17" s="3">
+        <v>2229</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>764</v>
+      </c>
+      <c r="W17" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="18" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="b" cm="1">
+        <f t="array" ref="G18">AND(K18:N18=S18:V18)</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L18" s="3">
+        <v>2229</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>788</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="R18" s="3">
+        <v>9</v>
+      </c>
+      <c r="S18" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T18" s="3">
+        <v>2229</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>788</v>
+      </c>
+      <c r="W18" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="19" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G19" s="2" t="b" cm="1">
+        <f t="array" ref="G19">AND(K19:N19=S19:V19)</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
+        <v>10</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L19" s="3">
+        <v>2229</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>800</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R19" s="3">
+        <v>10</v>
+      </c>
+      <c r="S19" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T19" s="3">
+        <v>2229</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <v>800</v>
+      </c>
+      <c r="W19" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="20" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="b" cm="1">
+        <f t="array" ref="G20">AND(K20:N20=S20:V20)</f>
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
+        <v>11</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L20" s="3">
+        <v>2232</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>796</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="R20" s="3">
+        <v>11</v>
+      </c>
+      <c r="S20" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T20" s="3">
+        <v>2232</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>796</v>
+      </c>
+      <c r="W20" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="21" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G21" s="2" t="b" cm="1">
+        <f t="array" ref="G21">AND(K21:N21=S21:V21)</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3">
+        <v>12</v>
+      </c>
+      <c r="K21" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L21" s="3">
+        <v>2229</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>805</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="R21" s="3">
+        <v>12</v>
+      </c>
+      <c r="S21" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2229</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>805</v>
+      </c>
+      <c r="W21" s="1">
+        <f t="shared" si="0"/>
+        <v>60.030999826267362</v>
+      </c>
+    </row>
+    <row r="22" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="b" cm="1">
+        <f t="array" ref="G22">AND(K22:N22=S22:V22)</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <v>13</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L22" s="3">
+        <v>2224</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>820</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="R22" s="3">
+        <v>13</v>
+      </c>
+      <c r="S22" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T22" s="3">
+        <v>2224</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>820</v>
+      </c>
+      <c r="W22" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="23" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G23" s="2" t="b" cm="1">
+        <f t="array" ref="G23">AND(K23:N23=S23:V23)</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
+        <v>14</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2220</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>832</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="R23" s="3">
+        <v>14</v>
+      </c>
+      <c r="S23" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T23" s="3">
+        <v>2220</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <v>832</v>
+      </c>
+      <c r="W23" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="24" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G24" s="2" t="b" cm="1">
+        <f t="array" ref="G24">AND(K24:N24=S24:V24)</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3">
+        <v>15</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2240</v>
+      </c>
+      <c r="M24" s="3">
+        <v>9</v>
+      </c>
+      <c r="N24" s="3">
+        <v>831</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="3">
+        <v>15</v>
+      </c>
+      <c r="S24" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T24" s="3">
+        <v>2240</v>
+      </c>
+      <c r="U24" s="3">
+        <v>9</v>
+      </c>
+      <c r="V24" s="3">
+        <v>831</v>
+      </c>
+      <c r="W24" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="25" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G25" s="2" t="b" cm="1">
+        <f t="array" ref="G25">AND(K25:N25=S25:V25)</f>
+        <v>1</v>
+      </c>
+      <c r="J25" s="3">
+        <v>16</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L25" s="3">
+        <v>2235</v>
+      </c>
+      <c r="M25" s="3">
+        <v>14</v>
+      </c>
+      <c r="N25" s="3">
+        <v>819</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="R25" s="3">
+        <v>16</v>
+      </c>
+      <c r="S25" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T25" s="3">
+        <v>2235</v>
+      </c>
+      <c r="U25" s="3">
+        <v>14</v>
+      </c>
+      <c r="V25" s="3">
+        <v>819</v>
+      </c>
+      <c r="W25" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="26" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="b" cm="1">
+        <f t="array" ref="G26">AND(K26:N26=S26:V26)</f>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
+        <v>17</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L26" s="3">
+        <v>2224</v>
+      </c>
+      <c r="M26" s="3">
+        <v>14</v>
+      </c>
+      <c r="N26" s="3">
+        <v>820</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="R26" s="3">
+        <v>17</v>
+      </c>
+      <c r="S26" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T26" s="3">
+        <v>2224</v>
+      </c>
+      <c r="U26" s="3">
+        <v>14</v>
+      </c>
+      <c r="V26" s="3">
+        <v>820</v>
+      </c>
+      <c r="W26" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="27" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G27" s="2" t="b" cm="1">
+        <f t="array" ref="G27">AND(K27:N27=S27:V27)</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
+        <v>18</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L27" s="3">
+        <v>2210</v>
+      </c>
+      <c r="M27" s="3">
+        <v>14</v>
+      </c>
+      <c r="N27" s="3">
+        <v>816</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="R27" s="3">
+        <v>18</v>
+      </c>
+      <c r="S27" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T27" s="3">
+        <v>2210</v>
+      </c>
+      <c r="U27" s="3">
+        <v>14</v>
+      </c>
+      <c r="V27" s="3">
+        <v>816</v>
+      </c>
+      <c r="W27" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="28" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G28" s="2" t="b" cm="1">
+        <f t="array" ref="G28">AND(K28:N28=S28:V28)</f>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
+        <v>19</v>
+      </c>
+      <c r="K28" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L28" s="3">
+        <v>2210</v>
+      </c>
+      <c r="M28" s="3">
+        <v>14</v>
+      </c>
+      <c r="N28" s="3">
+        <v>817</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="R28" s="3">
+        <v>19</v>
+      </c>
+      <c r="S28" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T28" s="3">
+        <v>2210</v>
+      </c>
+      <c r="U28" s="3">
+        <v>14</v>
+      </c>
+      <c r="V28" s="3">
+        <v>817</v>
+      </c>
+      <c r="W28" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="29" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G29" s="2" t="b" cm="1">
+        <f t="array" ref="G29">AND(K29:N29=S29:V29)</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3">
+        <v>20</v>
+      </c>
+      <c r="K29" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L29" s="3">
+        <v>2215</v>
+      </c>
+      <c r="M29" s="3">
+        <v>14</v>
+      </c>
+      <c r="N29" s="3">
+        <v>831</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="R29" s="3">
+        <v>20</v>
+      </c>
+      <c r="S29" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T29" s="3">
+        <v>2215</v>
+      </c>
+      <c r="U29" s="3">
+        <v>14</v>
+      </c>
+      <c r="V29" s="3">
+        <v>831</v>
+      </c>
+      <c r="W29" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="30" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G30" s="2" t="b" cm="1">
+        <f t="array" ref="G30">AND(K30:N30=S30:V30)</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3">
+        <v>21</v>
+      </c>
+      <c r="K30" s="3">
+        <v>2055</v>
+      </c>
+      <c r="L30" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M30" s="3">
+        <v>14</v>
+      </c>
+      <c r="N30" s="3">
+        <v>836</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="R30" s="3">
+        <v>21</v>
+      </c>
+      <c r="S30" s="3">
+        <v>2055</v>
+      </c>
+      <c r="T30" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U30" s="3">
+        <v>14</v>
+      </c>
+      <c r="V30" s="3">
+        <v>836</v>
+      </c>
+      <c r="W30" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="31" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G31" s="2" t="b" cm="1">
+        <f t="array" ref="G31">AND(K31:N31=S31:V31)</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="3">
+        <v>22</v>
+      </c>
+      <c r="K31" s="3">
+        <v>2055</v>
+      </c>
+      <c r="L31" s="3">
+        <v>2215</v>
+      </c>
+      <c r="M31" s="3">
+        <v>7</v>
+      </c>
+      <c r="N31" s="3">
+        <v>856</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="R31" s="3">
+        <v>22</v>
+      </c>
+      <c r="S31" s="3">
+        <v>2055</v>
+      </c>
+      <c r="T31" s="3">
+        <v>2215</v>
+      </c>
+      <c r="U31" s="3">
+        <v>7</v>
+      </c>
+      <c r="V31" s="3">
+        <v>856</v>
+      </c>
+      <c r="W31" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="32" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G32" s="2" t="b" cm="1">
+        <f t="array" ref="G32">AND(K32:N32=S32:V32)</f>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3">
+        <v>23</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2050</v>
+      </c>
+      <c r="L32" s="3">
+        <v>2207</v>
+      </c>
+      <c r="M32" s="3">
+        <v>14</v>
+      </c>
+      <c r="N32" s="3">
+        <v>859</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="R32" s="3">
+        <v>23</v>
+      </c>
+      <c r="S32" s="3">
+        <v>2050</v>
+      </c>
+      <c r="T32" s="3">
+        <v>2207</v>
+      </c>
+      <c r="U32" s="3">
+        <v>14</v>
+      </c>
+      <c r="V32" s="3">
+        <v>859</v>
+      </c>
+      <c r="W32" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="33" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G33" s="2" t="b" cm="1">
+        <f t="array" ref="G33">AND(K33:N33=S33:V33)</f>
+        <v>1</v>
+      </c>
+      <c r="J33" s="3">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>14</v>
+      </c>
+      <c r="N33" s="3">
+        <v>849</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R33" s="3">
+        <v>24</v>
+      </c>
+      <c r="S33" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U33" s="3">
+        <v>14</v>
+      </c>
+      <c r="V33" s="3">
+        <v>849</v>
+      </c>
+      <c r="W33" s="1">
+        <f t="shared" si="0"/>
+        <v>60.030000284314156</v>
+      </c>
+    </row>
+    <row r="34" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G34" s="2" t="b" cm="1">
+        <f t="array" ref="G34">AND(K34:N34=S34:V34)</f>
+        <v>1</v>
+      </c>
+      <c r="J34" s="3">
+        <v>25</v>
+      </c>
+      <c r="K34" s="3">
+        <v>2055</v>
+      </c>
+      <c r="L34" s="3">
+        <v>2208</v>
+      </c>
+      <c r="M34" s="3">
+        <v>7</v>
+      </c>
+      <c r="N34" s="3">
+        <v>865</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R34" s="3">
+        <v>25</v>
+      </c>
+      <c r="S34" s="3">
+        <v>2055</v>
+      </c>
+      <c r="T34" s="3">
+        <v>2208</v>
+      </c>
+      <c r="U34" s="3">
+        <v>7</v>
+      </c>
+      <c r="V34" s="3">
+        <v>865</v>
+      </c>
+      <c r="W34" s="1">
+        <f t="shared" si="0"/>
+        <v>59.968999936245382</v>
+      </c>
+    </row>
+    <row r="35" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G35" s="2" t="b" cm="1">
+        <f t="array" ref="G35">AND(K35:N35=S35:V35)</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="3">
+        <v>26</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2057</v>
+      </c>
+      <c r="L35" s="3">
+        <v>2213</v>
+      </c>
+      <c r="M35" s="3">
+        <v>7</v>
+      </c>
+      <c r="N35" s="3">
+        <v>865</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R35" s="3">
+        <v>26</v>
+      </c>
+      <c r="S35" s="3">
+        <v>2057</v>
+      </c>
+      <c r="T35" s="3">
+        <v>2213</v>
+      </c>
+      <c r="U35" s="3">
+        <v>7</v>
+      </c>
+      <c r="V35" s="3">
+        <v>865</v>
+      </c>
+      <c r="W35" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001999908126891</v>
+      </c>
+    </row>
+    <row r="36" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G36" s="2" t="b" cm="1">
+        <f t="array" ref="G36">AND(K36:N36=S36:V36)</f>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <v>27</v>
+      </c>
+      <c r="K36" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L36" s="3">
+        <v>2194</v>
+      </c>
+      <c r="M36" s="3">
+        <v>6</v>
+      </c>
+      <c r="N36" s="3">
+        <v>909</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="R36" s="3">
+        <v>27</v>
+      </c>
+      <c r="S36" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T36" s="3">
+        <v>2194</v>
+      </c>
+      <c r="U36" s="3">
+        <v>6</v>
+      </c>
+      <c r="V36" s="3">
+        <v>909</v>
+      </c>
+      <c r="W36" s="1">
+        <f t="shared" si="0"/>
+        <v>60.030999826267362</v>
+      </c>
+    </row>
+    <row r="37" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G37" s="2" t="b" cm="1">
+        <f t="array" ref="G37">AND(K37:N37=S37:V37)</f>
+        <v>1</v>
+      </c>
+      <c r="J37" s="3">
+        <v>28</v>
+      </c>
+      <c r="K37" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L37" s="3">
+        <v>2189</v>
+      </c>
+      <c r="M37" s="3">
+        <v>6</v>
+      </c>
+      <c r="N37" s="3">
+        <v>913</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="R37" s="3">
+        <v>28</v>
+      </c>
+      <c r="S37" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T37" s="3">
+        <v>2189</v>
+      </c>
+      <c r="U37" s="3">
+        <v>6</v>
+      </c>
+      <c r="V37" s="3">
+        <v>913</v>
+      </c>
+      <c r="W37" s="1">
+        <f>(DATEVALUE(LEFT(Q37,10))+TIMEVALUE(MID(Q37,12,12)) - (DATEVALUE(LEFT(Q36,10))+TIMEVALUE(MID(Q36,12,12)))) * 86400</f>
+        <v>59.970000106841326</v>
+      </c>
+    </row>
+    <row r="38" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G38" s="2" t="b" cm="1">
+        <f t="array" ref="G38">AND(K38:N38=S38:V38)</f>
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <v>29</v>
+      </c>
+      <c r="K38" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L38" s="3">
+        <v>2197</v>
+      </c>
+      <c r="M38" s="3">
+        <v>6</v>
+      </c>
+      <c r="N38" s="3">
+        <v>927</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="R38" s="3">
+        <v>29</v>
+      </c>
+      <c r="S38" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T38" s="3">
+        <v>2197</v>
+      </c>
+      <c r="U38" s="3">
+        <v>6</v>
+      </c>
+      <c r="V38" s="3">
+        <v>927</v>
+      </c>
+      <c r="W38" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="39" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G39" s="2" t="b" cm="1">
+        <f t="array" ref="G39">AND(K39:N39=S39:V39)</f>
+        <v>1</v>
+      </c>
+      <c r="J39" s="3">
+        <v>30</v>
+      </c>
+      <c r="K39" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L39" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M39" s="3">
+        <v>6</v>
+      </c>
+      <c r="N39" s="3">
+        <v>1099</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="R39" s="3">
+        <v>30</v>
+      </c>
+      <c r="S39" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T39" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U39" s="3">
+        <v>6</v>
+      </c>
+      <c r="V39" s="3">
+        <v>1099</v>
+      </c>
+      <c r="W39" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="40" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G40" s="2" t="b" cm="1">
+        <f t="array" ref="G40">AND(K40:N40=S40:V40)</f>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3">
+        <v>31</v>
+      </c>
+      <c r="K40" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L40" s="3">
+        <v>2213</v>
+      </c>
+      <c r="M40" s="3">
+        <v>6</v>
+      </c>
+      <c r="N40" s="3">
+        <v>1422</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="R40" s="3">
+        <v>31</v>
+      </c>
+      <c r="S40" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T40" s="3">
+        <v>2213</v>
+      </c>
+      <c r="U40" s="3">
+        <v>6</v>
+      </c>
+      <c r="V40" s="3">
+        <v>1422</v>
+      </c>
+      <c r="W40" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="41" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G41" s="2" t="b" cm="1">
+        <f t="array" ref="G41">AND(K41:N41=S41:V41)</f>
+        <v>1</v>
+      </c>
+      <c r="J41" s="3">
+        <v>32</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L41" s="3">
+        <v>2252</v>
+      </c>
+      <c r="M41" s="3">
+        <v>6</v>
+      </c>
+      <c r="N41" s="3">
+        <v>917</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="R41" s="3">
+        <v>32</v>
+      </c>
+      <c r="S41" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T41" s="3">
+        <v>2252</v>
+      </c>
+      <c r="U41" s="3">
+        <v>6</v>
+      </c>
+      <c r="V41" s="3">
+        <v>917</v>
+      </c>
+      <c r="W41" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="42" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G42" s="2" t="b" cm="1">
+        <f t="array" ref="G42">AND(K42:N42=S42:V42)</f>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3">
+        <v>33</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L42" s="3">
+        <v>2205</v>
+      </c>
+      <c r="M42" s="3">
+        <v>10</v>
+      </c>
+      <c r="N42" s="3">
+        <v>1003</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="R42" s="3">
+        <v>33</v>
+      </c>
+      <c r="S42" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T42" s="3">
+        <v>2205</v>
+      </c>
+      <c r="U42" s="3">
+        <v>10</v>
+      </c>
+      <c r="V42" s="3">
+        <v>1003</v>
+      </c>
+      <c r="W42" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="43" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G43" s="2" t="b" cm="1">
+        <f t="array" ref="G43">AND(K43:N43=S43:V43)</f>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3">
+        <v>34</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L43" s="3">
+        <v>2193</v>
+      </c>
+      <c r="M43" s="3">
+        <v>24</v>
+      </c>
+      <c r="N43" s="3">
+        <v>1051</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R43" s="3">
+        <v>34</v>
+      </c>
+      <c r="S43" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T43" s="3">
+        <v>2193</v>
+      </c>
+      <c r="U43" s="3">
+        <v>24</v>
+      </c>
+      <c r="V43" s="3">
+        <v>1051</v>
+      </c>
+      <c r="W43" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="44" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G44" s="2" t="b" cm="1">
+        <f t="array" ref="G44">AND(K44:N44=S44:V44)</f>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3">
+        <v>35</v>
+      </c>
+      <c r="K44" s="3">
+        <v>2058</v>
+      </c>
+      <c r="L44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M44" s="3">
+        <v>24</v>
+      </c>
+      <c r="N44" s="3">
+        <v>836</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R44" s="3">
+        <v>35</v>
+      </c>
+      <c r="S44" s="3">
+        <v>2058</v>
+      </c>
+      <c r="T44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U44" s="3">
+        <v>24</v>
+      </c>
+      <c r="V44" s="3">
+        <v>836</v>
+      </c>
+      <c r="W44" s="1">
+        <f t="shared" si="0"/>
+        <v>60.029999655671418</v>
+      </c>
+    </row>
+    <row r="45" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G45" s="2" t="b" cm="1">
+        <f t="array" ref="G45">AND(K45:N45=S45:V45)</f>
+        <v>1</v>
+      </c>
+      <c r="J45" s="3">
+        <v>36</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2194</v>
+      </c>
+      <c r="M45" s="3">
+        <v>14</v>
+      </c>
+      <c r="N45" s="3">
+        <v>820</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="R45" s="3">
+        <v>36</v>
+      </c>
+      <c r="S45" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T45" s="3">
+        <v>2194</v>
+      </c>
+      <c r="U45" s="3">
+        <v>14</v>
+      </c>
+      <c r="V45" s="3">
+        <v>820</v>
+      </c>
+      <c r="W45" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="46" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G46" s="2" t="b" cm="1">
+        <f t="array" ref="G46">AND(K46:N46=S46:V46)</f>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3">
+        <v>37</v>
+      </c>
+      <c r="K46" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L46" s="3">
+        <v>2224</v>
+      </c>
+      <c r="M46" s="3">
+        <v>14</v>
+      </c>
+      <c r="N46" s="3">
+        <v>782</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="R46" s="3">
+        <v>37</v>
+      </c>
+      <c r="S46" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T46" s="3">
+        <v>2224</v>
+      </c>
+      <c r="U46" s="3">
+        <v>14</v>
+      </c>
+      <c r="V46" s="3">
+        <v>782</v>
+      </c>
+      <c r="W46" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="47" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G47" s="2" t="b" cm="1">
+        <f t="array" ref="G47">AND(K47:N47=S47:V47)</f>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3">
+        <v>38</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2057</v>
+      </c>
+      <c r="L47" s="3">
+        <v>2210</v>
+      </c>
+      <c r="M47" s="3">
+        <v>10</v>
+      </c>
+      <c r="N47" s="3">
+        <v>914</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="R47" s="3">
+        <v>38</v>
+      </c>
+      <c r="S47" s="3">
+        <v>2057</v>
+      </c>
+      <c r="T47" s="3">
+        <v>2210</v>
+      </c>
+      <c r="U47" s="3">
+        <v>10</v>
+      </c>
+      <c r="V47" s="3">
+        <v>914</v>
+      </c>
+      <c r="W47" s="1">
+        <f t="shared" si="0"/>
+        <v>60.029999655671418</v>
+      </c>
+    </row>
+    <row r="48" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G48" s="2" t="b" cm="1">
+        <f t="array" ref="G48">AND(K48:N48=S48:V48)</f>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3">
+        <v>39</v>
+      </c>
+      <c r="K48" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L48" s="3">
+        <v>2220</v>
+      </c>
+      <c r="M48" s="3">
+        <v>10</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1018</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="R48" s="3">
+        <v>39</v>
+      </c>
+      <c r="S48" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T48" s="3">
+        <v>2220</v>
+      </c>
+      <c r="U48" s="3">
+        <v>10</v>
+      </c>
+      <c r="V48" s="3">
+        <v>1018</v>
+      </c>
+      <c r="W48" s="1">
+        <f t="shared" si="0"/>
+        <v>59.970000106841326</v>
+      </c>
+    </row>
+    <row r="49" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G49" s="2" t="b" cm="1">
+        <f t="array" ref="G49">AND(K49:N49=S49:V49)</f>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3">
+        <v>40</v>
+      </c>
+      <c r="K49" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L49" s="3">
+        <v>2250</v>
+      </c>
+      <c r="M49" s="3">
+        <v>9</v>
+      </c>
+      <c r="N49" s="3">
+        <v>806</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="R49" s="3">
+        <v>40</v>
+      </c>
+      <c r="S49" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T49" s="3">
+        <v>2250</v>
+      </c>
+      <c r="U49" s="3">
+        <v>9</v>
+      </c>
+      <c r="V49" s="3">
+        <v>806</v>
+      </c>
+      <c r="W49" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+    </row>
+    <row r="50" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G50" s="2" t="b" cm="1">
+        <f t="array" ref="G50">AND(K50:N50=S50:V50)</f>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3">
+        <v>41</v>
+      </c>
+      <c r="K50" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L50" s="3">
+        <v>2214</v>
+      </c>
+      <c r="M50" s="3">
+        <v>9</v>
+      </c>
+      <c r="N50" s="3">
+        <v>673</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="R50" s="3">
+        <v>41</v>
+      </c>
+      <c r="S50" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T50" s="3">
+        <v>2214</v>
+      </c>
+      <c r="U50" s="3">
+        <v>9</v>
+      </c>
+      <c r="V50" s="3">
+        <v>673</v>
+      </c>
+      <c r="W50" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="51" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G51" s="2" t="b" cm="1">
+        <f t="array" ref="G51">AND(K51:N51=S51:V51)</f>
+        <v>1</v>
+      </c>
+      <c r="J51" s="3">
+        <v>42</v>
+      </c>
+      <c r="K51" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L51" s="3">
+        <v>2205</v>
+      </c>
+      <c r="M51" s="3">
+        <v>9</v>
+      </c>
+      <c r="N51" s="3">
+        <v>660</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R51" s="3">
+        <v>42</v>
+      </c>
+      <c r="S51" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T51" s="3">
+        <v>2205</v>
+      </c>
+      <c r="U51" s="3">
+        <v>9</v>
+      </c>
+      <c r="V51" s="3">
+        <v>660</v>
+      </c>
+      <c r="W51" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="52" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G52" s="2" t="b" cm="1">
+        <f t="array" ref="G52">AND(K52:N52=S52:V52)</f>
+        <v>1</v>
+      </c>
+      <c r="J52" s="3">
+        <v>43</v>
+      </c>
+      <c r="K52" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L52" s="3">
+        <v>2220</v>
+      </c>
+      <c r="M52" s="3">
+        <v>358</v>
+      </c>
+      <c r="N52" s="3">
+        <v>647</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="R52" s="3">
+        <v>43</v>
+      </c>
+      <c r="S52" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T52" s="3">
+        <v>2220</v>
+      </c>
+      <c r="U52" s="3">
+        <v>358</v>
+      </c>
+      <c r="V52" s="3">
+        <v>647</v>
+      </c>
+      <c r="W52" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="53" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G53" s="2" t="b" cm="1">
+        <f t="array" ref="G53">AND(K53:N53=S53:V53)</f>
+        <v>1</v>
+      </c>
+      <c r="J53" s="3">
+        <v>44</v>
+      </c>
+      <c r="K53" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L53" s="3">
+        <v>2202</v>
+      </c>
+      <c r="M53" s="3">
+        <v>438</v>
+      </c>
+      <c r="N53" s="3">
+        <v>649</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R53" s="3">
+        <v>44</v>
+      </c>
+      <c r="S53" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T53" s="3">
+        <v>2202</v>
+      </c>
+      <c r="U53" s="3">
+        <v>438</v>
+      </c>
+      <c r="V53" s="3">
+        <v>649</v>
+      </c>
+      <c r="W53" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="54" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G54" s="2" t="b" cm="1">
+        <f t="array" ref="G54">AND(K54:N54=S54:V54)</f>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3">
+        <v>45</v>
+      </c>
+      <c r="K54" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L54" s="3">
+        <v>2186</v>
+      </c>
+      <c r="M54" s="3">
+        <v>454</v>
+      </c>
+      <c r="N54" s="3">
+        <v>652</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="R54" s="3">
+        <v>45</v>
+      </c>
+      <c r="S54" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T54" s="3">
+        <v>2186</v>
+      </c>
+      <c r="U54" s="3">
+        <v>454</v>
+      </c>
+      <c r="V54" s="3">
+        <v>652</v>
+      </c>
+      <c r="W54" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="55" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G55" s="2" t="b" cm="1">
+        <f t="array" ref="G55">AND(K55:N55=S55:V55)</f>
+        <v>1</v>
+      </c>
+      <c r="J55" s="3">
+        <v>46</v>
+      </c>
+      <c r="K55" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L55" s="3">
+        <v>2220</v>
+      </c>
+      <c r="M55" s="3">
+        <v>443</v>
+      </c>
+      <c r="N55" s="3">
+        <v>682</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="R55" s="3">
+        <v>46</v>
+      </c>
+      <c r="S55" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T55" s="3">
+        <v>2220</v>
+      </c>
+      <c r="U55" s="3">
+        <v>443</v>
+      </c>
+      <c r="V55" s="3">
+        <v>682</v>
+      </c>
+      <c r="W55" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="56" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G56" s="2" t="b" cm="1">
+        <f t="array" ref="G56">AND(K56:N56=S56:V56)</f>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3">
+        <v>47</v>
+      </c>
+      <c r="K56" s="3">
+        <v>2060</v>
+      </c>
+      <c r="L56" s="3">
+        <v>2226</v>
+      </c>
+      <c r="M56" s="3">
+        <v>444</v>
+      </c>
+      <c r="N56" s="3">
+        <v>702</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="R56" s="3">
+        <v>47</v>
+      </c>
+      <c r="S56" s="3">
+        <v>2060</v>
+      </c>
+      <c r="T56" s="3">
+        <v>2226</v>
+      </c>
+      <c r="U56" s="3">
+        <v>444</v>
+      </c>
+      <c r="V56" s="3">
+        <v>702</v>
+      </c>
+      <c r="W56" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="57" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G57" s="2" t="b" cm="1">
+        <f t="array" ref="G57">AND(K57:N57=S57:V57)</f>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3">
+        <v>48</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2063</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2226</v>
+      </c>
+      <c r="M57" s="3">
+        <v>444</v>
+      </c>
+      <c r="N57" s="3">
+        <v>707</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R57" s="3">
+        <v>48</v>
+      </c>
+      <c r="S57" s="3">
+        <v>2063</v>
+      </c>
+      <c r="T57" s="3">
+        <v>2226</v>
+      </c>
+      <c r="U57" s="3">
+        <v>444</v>
+      </c>
+      <c r="V57" s="3">
+        <v>707</v>
+      </c>
+      <c r="W57" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="58" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G58" s="2" t="b" cm="1">
+        <f t="array" ref="G58">AND(K58:N58=S58:V58)</f>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3">
+        <v>49</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2062</v>
+      </c>
+      <c r="L58" s="3">
+        <v>2210</v>
+      </c>
+      <c r="M58" s="3">
+        <v>440</v>
+      </c>
+      <c r="N58" s="3">
+        <v>698</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R58" s="3">
+        <v>49</v>
+      </c>
+      <c r="S58" s="3">
+        <v>2062</v>
+      </c>
+      <c r="T58" s="3">
+        <v>2210</v>
+      </c>
+      <c r="U58" s="3">
+        <v>440</v>
+      </c>
+      <c r="V58" s="3">
+        <v>698</v>
+      </c>
+      <c r="W58" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="59" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G59" s="2" t="b" cm="1">
+        <f t="array" ref="G59">AND(K59:N59=S59:V59)</f>
+        <v>1</v>
+      </c>
+      <c r="J59" s="3">
+        <v>50</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2067</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2217</v>
+      </c>
+      <c r="M59" s="3">
+        <v>437</v>
+      </c>
+      <c r="N59" s="3">
+        <v>692</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R59" s="3">
+        <v>50</v>
+      </c>
+      <c r="S59" s="3">
+        <v>2067</v>
+      </c>
+      <c r="T59" s="3">
+        <v>2217</v>
+      </c>
+      <c r="U59" s="3">
+        <v>437</v>
+      </c>
+      <c r="V59" s="3">
+        <v>692</v>
+      </c>
+      <c r="W59" s="1">
+        <f t="shared" si="0"/>
+        <v>60.030000284314156</v>
+      </c>
+    </row>
+    <row r="60" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G60" s="2" t="b" cm="1">
+        <f t="array" ref="G60">AND(K60:N60=S60:V60)</f>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3">
+        <v>51</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L60" s="3">
+        <v>2217</v>
+      </c>
+      <c r="M60" s="3">
+        <v>428</v>
+      </c>
+      <c r="N60" s="3">
+        <v>690</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="R60" s="3">
+        <v>51</v>
+      </c>
+      <c r="S60" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T60" s="3">
+        <v>2217</v>
+      </c>
+      <c r="U60" s="3">
+        <v>428</v>
+      </c>
+      <c r="V60" s="3">
+        <v>690</v>
+      </c>
+      <c r="W60" s="1">
+        <f t="shared" si="0"/>
+        <v>59.970999648794532</v>
+      </c>
+    </row>
+    <row r="61" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G61" s="2" t="b" cm="1">
+        <f t="array" ref="G61">AND(K61:N61=S61:V61)</f>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3">
+        <v>52</v>
+      </c>
+      <c r="K61" s="3">
+        <v>2067</v>
+      </c>
+      <c r="L61" s="3">
+        <v>2223</v>
+      </c>
+      <c r="M61" s="3">
+        <v>418</v>
+      </c>
+      <c r="N61" s="3">
+        <v>700</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="R61" s="3">
+        <v>52</v>
+      </c>
+      <c r="S61" s="3">
+        <v>2067</v>
+      </c>
+      <c r="T61" s="3">
+        <v>2223</v>
+      </c>
+      <c r="U61" s="3">
+        <v>418</v>
+      </c>
+      <c r="V61" s="3">
+        <v>700</v>
+      </c>
+      <c r="W61" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="62" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G62" s="2" t="b" cm="1">
+        <f t="array" ref="G62">AND(K62:N62=S62:V62)</f>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3">
+        <v>53</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2222</v>
+      </c>
+      <c r="M62" s="3">
+        <v>418</v>
+      </c>
+      <c r="N62" s="3">
+        <v>708</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="R62" s="3">
+        <v>53</v>
+      </c>
+      <c r="S62" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T62" s="3">
+        <v>2222</v>
+      </c>
+      <c r="U62" s="3">
+        <v>418</v>
+      </c>
+      <c r="V62" s="3">
+        <v>708</v>
+      </c>
+      <c r="W62" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+    </row>
+    <row r="63" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G63" s="2" t="b" cm="1">
+        <f t="array" ref="G63">AND(K63:N63=S63:V63)</f>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3">
+        <v>54</v>
+      </c>
+      <c r="K63" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L63" s="3">
+        <v>2232</v>
+      </c>
+      <c r="M63" s="3">
+        <v>418</v>
+      </c>
+      <c r="N63" s="3">
+        <v>717</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="R63" s="3">
+        <v>54</v>
+      </c>
+      <c r="S63" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T63" s="3">
+        <v>2232</v>
+      </c>
+      <c r="U63" s="3">
+        <v>418</v>
+      </c>
+      <c r="V63" s="3">
+        <v>717</v>
+      </c>
+      <c r="W63" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+    </row>
+    <row r="64" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G64" s="2" t="b" cm="1">
+        <f t="array" ref="G64">AND(K64:N64=S64:V64)</f>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3">
+        <v>55</v>
+      </c>
+      <c r="K64" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L64" s="3">
+        <v>2236</v>
+      </c>
+      <c r="M64" s="3">
+        <v>429</v>
+      </c>
+      <c r="N64" s="3">
         <v>723</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O64" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R64" s="3">
+        <v>55</v>
+      </c>
+      <c r="S64" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T64" s="3">
+        <v>2236</v>
+      </c>
+      <c r="U64" s="3">
+        <v>429</v>
+      </c>
+      <c r="V64" s="3">
+        <v>723</v>
+      </c>
+      <c r="W64" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+    </row>
+    <row r="65" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G65" s="2" t="b" cm="1">
+        <f t="array" ref="G65">AND(K65:N65=S65:V65)</f>
         <v>1</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T9" s="5">
-        <v>2280</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5">
-        <v>723</v>
+      <c r="J65" s="3">
+        <v>56</v>
+      </c>
+      <c r="K65" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L65" s="3">
+        <v>2272</v>
+      </c>
+      <c r="M65" s="3">
+        <v>434</v>
+      </c>
+      <c r="N65" s="3">
+        <v>727</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="R65" s="3">
+        <v>56</v>
+      </c>
+      <c r="S65" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T65" s="3">
+        <v>2272</v>
+      </c>
+      <c r="U65" s="3">
+        <v>434</v>
+      </c>
+      <c r="V65" s="3">
+        <v>727</v>
+      </c>
+      <c r="W65" s="1">
+        <f t="shared" si="0"/>
+        <v>60.029999655671418</v>
+      </c>
+      <c r="Y65" s="7" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="10" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F10" s="2"/>
-      <c r="J10" s="5">
+    <row r="66" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G66" s="2" t="b" cm="1">
+        <f t="array" ref="G66">AND(K66:N66=S66:V66)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L10" s="5">
-        <v>2250</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
-        <v>766</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="R10" s="5">
+      <c r="J66" s="3">
+        <v>57</v>
+      </c>
+      <c r="K66" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L66" s="3">
+        <v>2252</v>
+      </c>
+      <c r="M66" s="3">
+        <v>434</v>
+      </c>
+      <c r="N66" s="3">
+        <v>736</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="R66" s="3">
+        <v>57</v>
+      </c>
+      <c r="S66" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T66" s="3">
+        <v>2252</v>
+      </c>
+      <c r="U66" s="3">
+        <v>434</v>
+      </c>
+      <c r="V66" s="3">
+        <v>736</v>
+      </c>
+      <c r="W66" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
+      </c>
+      <c r="Y66" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z66" s="2">
+        <f>MIN(W10:W98)</f>
+        <v>59.968999936245382</v>
+      </c>
+    </row>
+    <row r="67" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G67" s="2" t="b" cm="1">
+        <f t="array" ref="G67">AND(K67:N67=S67:V67)</f>
         <v>1</v>
       </c>
-      <c r="S10" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T10" s="5">
-        <v>2250</v>
-      </c>
-      <c r="U10" s="5">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5">
-        <v>766</v>
+      <c r="J67" s="3">
+        <v>58</v>
+      </c>
+      <c r="K67" s="3">
+        <v>2070</v>
+      </c>
+      <c r="L67" s="3">
+        <v>2270</v>
+      </c>
+      <c r="M67" s="3">
+        <v>424</v>
+      </c>
+      <c r="N67" s="3">
+        <v>734</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="R67" s="3">
+        <v>58</v>
+      </c>
+      <c r="S67" s="3">
+        <v>2070</v>
+      </c>
+      <c r="T67" s="3">
+        <v>2270</v>
+      </c>
+      <c r="U67" s="3">
+        <v>424</v>
+      </c>
+      <c r="V67" s="3">
+        <v>734</v>
+      </c>
+      <c r="W67" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
+      </c>
+      <c r="Y67" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z67" s="2">
+        <f>MAX(W10:W98)</f>
+        <v>60.030999826267362</v>
       </c>
     </row>
-    <row r="11" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F11" s="2"/>
-      <c r="J11" s="5">
-        <v>2</v>
-      </c>
-      <c r="K11" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L11" s="5">
-        <v>2244</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <v>815</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="R11" s="5">
-        <v>2</v>
-      </c>
-      <c r="S11" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T11" s="5">
-        <v>2244</v>
-      </c>
-      <c r="U11" s="5">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5">
-        <v>815</v>
+    <row r="68" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G68" s="2" t="b" cm="1">
+        <f t="array" ref="G68">AND(K68:N68=S68:V68)</f>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3">
+        <v>59</v>
+      </c>
+      <c r="K68" s="3">
+        <v>2074</v>
+      </c>
+      <c r="L68" s="3">
+        <v>2262</v>
+      </c>
+      <c r="M68" s="3">
+        <v>438</v>
+      </c>
+      <c r="N68" s="3">
+        <v>734</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R68" s="3">
+        <v>59</v>
+      </c>
+      <c r="S68" s="3">
+        <v>2074</v>
+      </c>
+      <c r="T68" s="3">
+        <v>2262</v>
+      </c>
+      <c r="U68" s="3">
+        <v>438</v>
+      </c>
+      <c r="V68" s="3">
+        <v>734</v>
+      </c>
+      <c r="W68" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
+      </c>
+      <c r="Y68" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z68" s="2">
+        <f>AVERAGE(W10:W98)</f>
+        <v>60.001707864726441</v>
       </c>
     </row>
-    <row r="12" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F12" s="2"/>
-      <c r="J12" s="5">
-        <v>3</v>
-      </c>
-      <c r="K12" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2279</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
-        <v>844</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="5">
-        <v>3</v>
-      </c>
-      <c r="S12" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T12" s="5">
-        <v>2279</v>
-      </c>
-      <c r="U12" s="5">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5">
-        <v>844</v>
+    <row r="69" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G69" s="2" t="b" cm="1">
+        <f t="array" ref="G69">AND(K69:N69=S69:V69)</f>
+        <v>1</v>
+      </c>
+      <c r="J69" s="3">
+        <v>60</v>
+      </c>
+      <c r="K69" s="3">
+        <v>2074</v>
+      </c>
+      <c r="L69" s="3">
+        <v>2265</v>
+      </c>
+      <c r="M69" s="3">
+        <v>428</v>
+      </c>
+      <c r="N69" s="3">
+        <v>732</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="R69" s="3">
+        <v>60</v>
+      </c>
+      <c r="S69" s="3">
+        <v>2074</v>
+      </c>
+      <c r="T69" s="3">
+        <v>2265</v>
+      </c>
+      <c r="U69" s="3">
+        <v>428</v>
+      </c>
+      <c r="V69" s="3">
+        <v>732</v>
+      </c>
+      <c r="W69" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000999737530947</v>
+      </c>
+      <c r="Y69" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z69" s="2">
+        <f>_xlfn.STDEV.S(W10:W98)</f>
+        <v>1.1056856392346808E-2</v>
       </c>
     </row>
-    <row r="13" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F13" s="2"/>
-      <c r="J13" s="5">
-        <v>4</v>
-      </c>
-      <c r="K13" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2310</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5">
-        <v>844</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="R13" s="5">
-        <v>4</v>
-      </c>
-      <c r="S13" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T13" s="5">
-        <v>2310</v>
-      </c>
-      <c r="U13" s="5">
-        <v>0</v>
-      </c>
-      <c r="V13" s="5">
-        <v>844</v>
+    <row r="70" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G70" s="2" t="b" cm="1">
+        <f t="array" ref="G70">AND(K70:N70=S70:V70)</f>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3">
+        <v>61</v>
+      </c>
+      <c r="K70" s="3">
+        <v>2079</v>
+      </c>
+      <c r="L70" s="3">
+        <v>2260</v>
+      </c>
+      <c r="M70" s="3">
+        <v>438</v>
+      </c>
+      <c r="N70" s="3">
+        <v>732</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="R70" s="3">
+        <v>61</v>
+      </c>
+      <c r="S70" s="3">
+        <v>2079</v>
+      </c>
+      <c r="T70" s="3">
+        <v>2260</v>
+      </c>
+      <c r="U70" s="3">
+        <v>438</v>
+      </c>
+      <c r="V70" s="3">
+        <v>732</v>
+      </c>
+      <c r="W70" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
       </c>
     </row>
-    <row r="14" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F14" s="2"/>
-      <c r="J14" s="5">
-        <v>5</v>
-      </c>
-      <c r="K14" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L14" s="5">
-        <v>2254</v>
-      </c>
-      <c r="M14" s="5">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
-        <v>820</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="R14" s="5">
-        <v>5</v>
-      </c>
-      <c r="S14" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T14" s="5">
-        <v>2254</v>
-      </c>
-      <c r="U14" s="5">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5">
-        <v>820</v>
+    <row r="71" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G71" s="2" t="b" cm="1">
+        <f t="array" ref="G71">AND(K71:N71=S71:V71)</f>
+        <v>1</v>
+      </c>
+      <c r="J71" s="3">
+        <v>62</v>
+      </c>
+      <c r="K71" s="3">
+        <v>2086</v>
+      </c>
+      <c r="L71" s="3">
+        <v>2273</v>
+      </c>
+      <c r="M71" s="3">
+        <v>443</v>
+      </c>
+      <c r="N71" s="3">
+        <v>736</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="R71" s="3">
+        <v>62</v>
+      </c>
+      <c r="S71" s="3">
+        <v>2086</v>
+      </c>
+      <c r="T71" s="3">
+        <v>2273</v>
+      </c>
+      <c r="U71" s="3">
+        <v>443</v>
+      </c>
+      <c r="V71" s="3">
+        <v>736</v>
+      </c>
+      <c r="W71" s="1">
+        <f t="shared" si="0"/>
+        <v>60.000000195577741</v>
       </c>
     </row>
-    <row r="15" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F15" s="2"/>
-      <c r="J15" s="5">
-        <v>6</v>
-      </c>
-      <c r="K15" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L15" s="5">
-        <v>2244</v>
-      </c>
-      <c r="M15" s="5">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
-        <v>794</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="R15" s="5">
-        <v>6</v>
-      </c>
-      <c r="S15" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T15" s="5">
-        <v>2244</v>
-      </c>
-      <c r="U15" s="5">
-        <v>0</v>
-      </c>
-      <c r="V15" s="5">
-        <v>794</v>
+    <row r="72" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G72" s="2" t="b" cm="1">
+        <f t="array" ref="G72">AND(K72:N72=S72:V72)</f>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3">
+        <v>63</v>
+      </c>
+      <c r="K72" s="3">
+        <v>2089</v>
+      </c>
+      <c r="L72" s="3">
+        <v>2262</v>
+      </c>
+      <c r="M72" s="3">
+        <v>447</v>
+      </c>
+      <c r="N72" s="3">
+        <v>726</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="R72" s="3">
+        <v>63</v>
+      </c>
+      <c r="S72" s="3">
+        <v>2089</v>
+      </c>
+      <c r="T72" s="3">
+        <v>2262</v>
+      </c>
+      <c r="U72" s="3">
+        <v>447</v>
+      </c>
+      <c r="V72" s="3">
+        <v>726</v>
+      </c>
+      <c r="W72" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
       </c>
     </row>
-    <row r="16" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F16" s="2"/>
-      <c r="J16" s="5">
-        <v>7</v>
-      </c>
-      <c r="K16" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L16" s="5">
-        <v>2229</v>
-      </c>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5">
-        <v>762</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="R16" s="5">
-        <v>7</v>
-      </c>
-      <c r="S16" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T16" s="5">
-        <v>2229</v>
-      </c>
-      <c r="U16" s="5">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5">
-        <v>762</v>
+    <row r="73" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G73" s="2" t="b" cm="1">
+        <f t="array" ref="G73">AND(K73:N73=S73:V73)</f>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3">
+        <v>64</v>
+      </c>
+      <c r="K73" s="3">
+        <v>2092</v>
+      </c>
+      <c r="L73" s="3">
+        <v>2265</v>
+      </c>
+      <c r="M73" s="3">
+        <v>444</v>
+      </c>
+      <c r="N73" s="3">
+        <v>732</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="R73" s="3">
+        <v>64</v>
+      </c>
+      <c r="S73" s="3">
+        <v>2092</v>
+      </c>
+      <c r="T73" s="3">
+        <v>2265</v>
+      </c>
+      <c r="U73" s="3">
+        <v>444</v>
+      </c>
+      <c r="V73" s="3">
+        <v>732</v>
+      </c>
+      <c r="W73" s="1">
+        <f t="shared" si="0"/>
+        <v>60.001000366173685</v>
       </c>
     </row>
-    <row r="17" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F17" s="2"/>
-      <c r="J17" s="5">
-        <v>8</v>
-      </c>
-      <c r="K17" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L17" s="5">
-        <v>2229</v>
-      </c>
-      <c r="M17" s="5">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5">
-        <v>764</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="R17" s="5">
-        <v>8</v>
-      </c>
-      <c r="S17" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T17" s="5">
-        <v>2229</v>
-      </c>
-      <c r="U17" s="5">
-        <v>0</v>
-      </c>
-      <c r="V17" s="5">
-        <v>764</v>
+    <row r="74" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G74" s="2" t="b" cm="1">
+        <f t="array" ref="G74">AND(K74:N74=S74:V74)</f>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3">
+        <v>65</v>
+      </c>
+      <c r="K74" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L74" s="3">
+        <v>2270</v>
+      </c>
+      <c r="M74" s="3">
+        <v>447</v>
+      </c>
+      <c r="N74" s="3">
+        <v>735</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q74" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R74" s="3">
+        <v>65</v>
+      </c>
+      <c r="S74" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T74" s="3">
+        <v>2270</v>
+      </c>
+      <c r="U74" s="3">
+        <v>447</v>
+      </c>
+      <c r="V74" s="3">
+        <v>735</v>
+      </c>
+      <c r="W74" s="1">
+        <f t="shared" si="0"/>
+        <v>59.999999566935003</v>
       </c>
     </row>
-    <row r="18" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F18" s="2"/>
-      <c r="J18" s="5">
-        <v>9</v>
-      </c>
-      <c r="K18" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L18" s="5">
-        <v>2229</v>
-      </c>
-      <c r="M18" s="5">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5">
-        <v>788</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="R18" s="5">
-        <v>9</v>
-      </c>
-      <c r="S18" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T18" s="5">
-        <v>2229</v>
-      </c>
-      <c r="U18" s="5">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5">
-        <v>788</v>
+    <row r="75" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G75" s="2" t="b" cm="1">
+        <f t="array" ref="G75">AND(K75:N75=S75:V75)</f>
+        <v>1</v>
+      </c>
+      <c r="J75" s="3">
+        <v>66</v>
+      </c>
+      <c r="K75" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L75" s="3">
+        <v>2282</v>
+      </c>
+      <c r="M75" s="3">
+        <v>450</v>
+      </c>
+      <c r="N75" s="3">
+        <v>736</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="R75" s="3">
+        <v>66</v>
+      </c>
+      <c r="S75" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T75" s="3">
+        <v>2282</v>
+      </c>
+      <c r="U75" s="3">
+        <v>450</v>
+      </c>
+      <c r="V75" s="3">
+        <v>736</v>
+      </c>
+      <c r="W75" s="1">
+        <f t="shared" ref="W75:W98" si="1">(DATEVALUE(LEFT(Q75,10))+TIMEVALUE(MID(Q75,12,12)) - (DATEVALUE(LEFT(Q74,10))+TIMEVALUE(MID(Q74,12,12)))) * 86400</f>
+        <v>60.000000195577741</v>
       </c>
     </row>
-    <row r="19" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F19" s="2"/>
-      <c r="J19" s="5">
-        <v>10</v>
-      </c>
-      <c r="K19" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L19" s="5">
-        <v>2229</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
-        <v>800</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="R19" s="5">
-        <v>10</v>
-      </c>
-      <c r="S19" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T19" s="5">
-        <v>2229</v>
-      </c>
-      <c r="U19" s="5">
-        <v>0</v>
-      </c>
-      <c r="V19" s="5">
-        <v>800</v>
-      </c>
+    <row r="76" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G76" s="2" t="b" cm="1">
+        <f t="array" ref="G76">AND(K76:N76=S76:V76)</f>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3">
+        <v>67</v>
+      </c>
+      <c r="K76" s="3">
+        <v>2105</v>
+      </c>
+      <c r="L76" s="3">
+        <v>2329</v>
+      </c>
+      <c r="M76" s="3">
+        <v>436</v>
+      </c>
+      <c r="N76" s="3">
+        <v>812</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="R76" s="3">
+        <v>67</v>
+      </c>
+      <c r="S76" s="3">
+        <v>2105</v>
+      </c>
+      <c r="T76" s="3">
+        <v>2329</v>
+      </c>
+      <c r="U76" s="3">
+        <v>436</v>
+      </c>
+      <c r="V76" s="3">
+        <v>812</v>
+      </c>
+      <c r="W76" s="1">
+        <f t="shared" si="1"/>
+        <v>60.001000366173685</v>
+      </c>
+      <c r="Y76" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z76" s="9"/>
+      <c r="AA76" s="9"/>
+      <c r="AB76" s="9"/>
+      <c r="AC76" s="9"/>
+      <c r="AD76" s="9"/>
+      <c r="AE76" s="9"/>
+      <c r="AF76" s="9"/>
+      <c r="AG76" s="4"/>
     </row>
-    <row r="20" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F20" s="2"/>
-      <c r="J20" s="5">
-        <v>11</v>
-      </c>
-      <c r="K20" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L20" s="5">
-        <v>2232</v>
-      </c>
-      <c r="M20" s="5">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5">
-        <v>796</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="R20" s="5">
-        <v>11</v>
-      </c>
-      <c r="S20" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T20" s="5">
-        <v>2232</v>
-      </c>
-      <c r="U20" s="5">
-        <v>0</v>
-      </c>
-      <c r="V20" s="5">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="21" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F21" s="2"/>
-      <c r="J21" s="5">
-        <v>12</v>
-      </c>
-      <c r="K21" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L21" s="5">
-        <v>2229</v>
-      </c>
-      <c r="M21" s="5">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <v>805</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="R21" s="5">
-        <v>12</v>
-      </c>
-      <c r="S21" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T21" s="5">
-        <v>2229</v>
-      </c>
-      <c r="U21" s="5">
-        <v>0</v>
-      </c>
-      <c r="V21" s="5">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="22" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F22" s="2"/>
-      <c r="J22" s="5">
-        <v>13</v>
-      </c>
-      <c r="K22" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L22" s="5">
-        <v>2224</v>
-      </c>
-      <c r="M22" s="5">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5">
-        <v>820</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="R22" s="5">
-        <v>13</v>
-      </c>
-      <c r="S22" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T22" s="5">
-        <v>2224</v>
-      </c>
-      <c r="U22" s="5">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="23" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F23" s="2"/>
-      <c r="J23" s="5">
-        <v>14</v>
-      </c>
-      <c r="K23" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L23" s="5">
-        <v>2220</v>
-      </c>
-      <c r="M23" s="5">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
-        <v>832</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="R23" s="5">
-        <v>14</v>
-      </c>
-      <c r="S23" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T23" s="5">
-        <v>2220</v>
-      </c>
-      <c r="U23" s="5">
-        <v>0</v>
-      </c>
-      <c r="V23" s="5">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="24" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F24" s="2"/>
-      <c r="J24" s="5">
-        <v>15</v>
-      </c>
-      <c r="K24" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L24" s="5">
-        <v>2240</v>
-      </c>
-      <c r="M24" s="5">
-        <v>9</v>
-      </c>
-      <c r="N24" s="5">
-        <v>831</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="R24" s="5">
-        <v>15</v>
-      </c>
-      <c r="S24" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T24" s="5">
-        <v>2240</v>
-      </c>
-      <c r="U24" s="5">
-        <v>9</v>
-      </c>
-      <c r="V24" s="5">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="25" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F25" s="2"/>
-      <c r="J25" s="5">
-        <v>16</v>
-      </c>
-      <c r="K25" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L25" s="5">
-        <v>2235</v>
-      </c>
-      <c r="M25" s="5">
-        <v>14</v>
-      </c>
-      <c r="N25" s="5">
-        <v>819</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="R25" s="5">
-        <v>16</v>
-      </c>
-      <c r="S25" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T25" s="5">
-        <v>2235</v>
-      </c>
-      <c r="U25" s="5">
-        <v>14</v>
-      </c>
-      <c r="V25" s="5">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="26" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F26" s="2"/>
-      <c r="J26" s="5">
-        <v>17</v>
-      </c>
-      <c r="K26" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L26" s="5">
-        <v>2224</v>
-      </c>
-      <c r="M26" s="5">
-        <v>14</v>
-      </c>
-      <c r="N26" s="5">
-        <v>820</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="R26" s="5">
-        <v>17</v>
-      </c>
-      <c r="S26" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T26" s="5">
-        <v>2224</v>
-      </c>
-      <c r="U26" s="5">
-        <v>14</v>
-      </c>
-      <c r="V26" s="5">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="27" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F27" s="2"/>
-      <c r="J27" s="5">
-        <v>18</v>
-      </c>
-      <c r="K27" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L27" s="5">
-        <v>2210</v>
-      </c>
-      <c r="M27" s="5">
-        <v>14</v>
-      </c>
-      <c r="N27" s="5">
-        <v>816</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="R27" s="5">
-        <v>18</v>
-      </c>
-      <c r="S27" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T27" s="5">
-        <v>2210</v>
-      </c>
-      <c r="U27" s="5">
-        <v>14</v>
-      </c>
-      <c r="V27" s="5">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="28" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F28" s="2"/>
-      <c r="J28" s="5">
-        <v>19</v>
-      </c>
-      <c r="K28" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L28" s="5">
-        <v>2210</v>
-      </c>
-      <c r="M28" s="5">
-        <v>14</v>
-      </c>
-      <c r="N28" s="5">
-        <v>817</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="R28" s="5">
-        <v>19</v>
-      </c>
-      <c r="S28" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T28" s="5">
-        <v>2210</v>
-      </c>
-      <c r="U28" s="5">
-        <v>14</v>
-      </c>
-      <c r="V28" s="5">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="29" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F29" s="2"/>
-      <c r="J29" s="5">
-        <v>20</v>
-      </c>
-      <c r="K29" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L29" s="5">
-        <v>2215</v>
-      </c>
-      <c r="M29" s="5">
-        <v>14</v>
-      </c>
-      <c r="N29" s="5">
-        <v>831</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="R29" s="5">
-        <v>20</v>
-      </c>
-      <c r="S29" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T29" s="5">
-        <v>2215</v>
-      </c>
-      <c r="U29" s="5">
-        <v>14</v>
-      </c>
-      <c r="V29" s="5">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="30" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F30" s="2"/>
-      <c r="J30" s="5">
-        <v>21</v>
-      </c>
-      <c r="K30" s="5">
-        <v>2055</v>
-      </c>
-      <c r="L30" s="5">
-        <v>2200</v>
-      </c>
-      <c r="M30" s="5">
-        <v>14</v>
-      </c>
-      <c r="N30" s="5">
-        <v>836</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="R30" s="5">
-        <v>21</v>
-      </c>
-      <c r="S30" s="5">
-        <v>2055</v>
-      </c>
-      <c r="T30" s="5">
-        <v>2200</v>
-      </c>
-      <c r="U30" s="5">
-        <v>14</v>
-      </c>
-      <c r="V30" s="5">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="31" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F31" s="2"/>
-      <c r="J31" s="5">
-        <v>22</v>
-      </c>
-      <c r="K31" s="5">
-        <v>2055</v>
-      </c>
-      <c r="L31" s="5">
-        <v>2215</v>
-      </c>
-      <c r="M31" s="5">
-        <v>7</v>
-      </c>
-      <c r="N31" s="5">
-        <v>856</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="R31" s="5">
-        <v>22</v>
-      </c>
-      <c r="S31" s="5">
-        <v>2055</v>
-      </c>
-      <c r="T31" s="5">
-        <v>2215</v>
-      </c>
-      <c r="U31" s="5">
-        <v>7</v>
-      </c>
-      <c r="V31" s="5">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="32" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F32" s="2"/>
-      <c r="J32" s="5">
-        <v>23</v>
-      </c>
-      <c r="K32" s="5">
-        <v>2050</v>
-      </c>
-      <c r="L32" s="5">
-        <v>2207</v>
-      </c>
-      <c r="M32" s="5">
-        <v>14</v>
-      </c>
-      <c r="N32" s="5">
-        <v>859</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="R32" s="5">
-        <v>23</v>
-      </c>
-      <c r="S32" s="5">
-        <v>2050</v>
-      </c>
-      <c r="T32" s="5">
-        <v>2207</v>
-      </c>
-      <c r="U32" s="5">
-        <v>14</v>
-      </c>
-      <c r="V32" s="5">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="33" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F33" s="2"/>
-      <c r="J33" s="5">
-        <v>24</v>
-      </c>
-      <c r="K33" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L33" s="5">
-        <v>2200</v>
-      </c>
-      <c r="M33" s="5">
-        <v>14</v>
-      </c>
-      <c r="N33" s="5">
-        <v>849</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="R33" s="5">
-        <v>24</v>
-      </c>
-      <c r="S33" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T33" s="5">
-        <v>2200</v>
-      </c>
-      <c r="U33" s="5">
-        <v>14</v>
-      </c>
-      <c r="V33" s="5">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="34" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F34" s="2"/>
-      <c r="J34" s="5">
-        <v>25</v>
-      </c>
-      <c r="K34" s="5">
-        <v>2055</v>
-      </c>
-      <c r="L34" s="5">
-        <v>2208</v>
-      </c>
-      <c r="M34" s="5">
-        <v>7</v>
-      </c>
-      <c r="N34" s="5">
-        <v>865</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="R34" s="5">
-        <v>25</v>
-      </c>
-      <c r="S34" s="5">
-        <v>2055</v>
-      </c>
-      <c r="T34" s="5">
-        <v>2208</v>
-      </c>
-      <c r="U34" s="5">
-        <v>7</v>
-      </c>
-      <c r="V34" s="5">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="35" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F35" s="2"/>
-      <c r="J35" s="5">
-        <v>26</v>
-      </c>
-      <c r="K35" s="5">
-        <v>2057</v>
-      </c>
-      <c r="L35" s="5">
-        <v>2213</v>
-      </c>
-      <c r="M35" s="5">
-        <v>7</v>
-      </c>
-      <c r="N35" s="5">
-        <v>865</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="R35" s="5">
-        <v>26</v>
-      </c>
-      <c r="S35" s="5">
-        <v>2057</v>
-      </c>
-      <c r="T35" s="5">
-        <v>2213</v>
-      </c>
-      <c r="U35" s="5">
-        <v>7</v>
-      </c>
-      <c r="V35" s="5">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="36" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F36" s="2"/>
-      <c r="J36" s="5">
-        <v>27</v>
-      </c>
-      <c r="K36" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L36" s="5">
-        <v>2194</v>
-      </c>
-      <c r="M36" s="5">
-        <v>6</v>
-      </c>
-      <c r="N36" s="5">
-        <v>909</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="R36" s="5">
-        <v>27</v>
-      </c>
-      <c r="S36" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T36" s="5">
-        <v>2194</v>
-      </c>
-      <c r="U36" s="5">
-        <v>6</v>
-      </c>
-      <c r="V36" s="5">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="37" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F37" s="2"/>
-      <c r="J37" s="5">
-        <v>28</v>
-      </c>
-      <c r="K37" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L37" s="5">
-        <v>2189</v>
-      </c>
-      <c r="M37" s="5">
-        <v>6</v>
-      </c>
-      <c r="N37" s="5">
-        <v>913</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q37" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="R37" s="5">
-        <v>28</v>
-      </c>
-      <c r="S37" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T37" s="5">
-        <v>2189</v>
-      </c>
-      <c r="U37" s="5">
-        <v>6</v>
-      </c>
-      <c r="V37" s="5">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="38" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F38" s="2"/>
-      <c r="J38" s="5">
-        <v>29</v>
-      </c>
-      <c r="K38" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L38" s="5">
-        <v>2197</v>
-      </c>
-      <c r="M38" s="5">
-        <v>6</v>
-      </c>
-      <c r="N38" s="5">
-        <v>927</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R38" s="5">
-        <v>29</v>
-      </c>
-      <c r="S38" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T38" s="5">
-        <v>2197</v>
-      </c>
-      <c r="U38" s="5">
-        <v>6</v>
-      </c>
-      <c r="V38" s="5">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="39" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F39" s="2"/>
-      <c r="J39" s="5">
-        <v>30</v>
-      </c>
-      <c r="K39" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L39" s="5">
-        <v>2200</v>
-      </c>
-      <c r="M39" s="5">
-        <v>6</v>
-      </c>
-      <c r="N39" s="5">
-        <v>1099</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="R39" s="5">
-        <v>30</v>
-      </c>
-      <c r="S39" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T39" s="5">
-        <v>2200</v>
-      </c>
-      <c r="U39" s="5">
-        <v>6</v>
-      </c>
-      <c r="V39" s="5">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="40" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F40" s="2"/>
-      <c r="J40" s="5">
-        <v>31</v>
-      </c>
-      <c r="K40" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L40" s="5">
-        <v>2213</v>
-      </c>
-      <c r="M40" s="5">
-        <v>6</v>
-      </c>
-      <c r="N40" s="5">
-        <v>1422</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="R40" s="5">
-        <v>31</v>
-      </c>
-      <c r="S40" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T40" s="5">
-        <v>2213</v>
-      </c>
-      <c r="U40" s="5">
-        <v>6</v>
-      </c>
-      <c r="V40" s="5">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="41" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F41" s="2"/>
-      <c r="J41" s="5">
-        <v>32</v>
-      </c>
-      <c r="K41" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L41" s="5">
-        <v>2252</v>
-      </c>
-      <c r="M41" s="5">
-        <v>6</v>
-      </c>
-      <c r="N41" s="5">
-        <v>917</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q41" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="R41" s="5">
-        <v>32</v>
-      </c>
-      <c r="S41" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T41" s="5">
-        <v>2252</v>
-      </c>
-      <c r="U41" s="5">
-        <v>6</v>
-      </c>
-      <c r="V41" s="5">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="42" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F42" s="2"/>
-      <c r="J42" s="5">
-        <v>33</v>
-      </c>
-      <c r="K42" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L42" s="5">
-        <v>2205</v>
-      </c>
-      <c r="M42" s="5">
-        <v>10</v>
-      </c>
-      <c r="N42" s="5">
-        <v>1003</v>
-      </c>
-      <c r="O42" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="R42" s="5">
-        <v>33</v>
-      </c>
-      <c r="S42" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T42" s="5">
-        <v>2205</v>
-      </c>
-      <c r="U42" s="5">
-        <v>10</v>
-      </c>
-      <c r="V42" s="5">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="43" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F43" s="2"/>
-      <c r="J43" s="5">
-        <v>34</v>
-      </c>
-      <c r="K43" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L43" s="5">
-        <v>2193</v>
-      </c>
-      <c r="M43" s="5">
-        <v>24</v>
-      </c>
-      <c r="N43" s="5">
-        <v>1051</v>
-      </c>
-      <c r="O43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="R43" s="5">
-        <v>34</v>
-      </c>
-      <c r="S43" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T43" s="5">
-        <v>2193</v>
-      </c>
-      <c r="U43" s="5">
-        <v>24</v>
-      </c>
-      <c r="V43" s="5">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="44" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F44" s="2"/>
-      <c r="J44" s="5">
-        <v>35</v>
-      </c>
-      <c r="K44" s="5">
-        <v>2058</v>
-      </c>
-      <c r="L44" s="5">
-        <v>2200</v>
-      </c>
-      <c r="M44" s="5">
-        <v>24</v>
-      </c>
-      <c r="N44" s="5">
-        <v>836</v>
-      </c>
-      <c r="O44" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q44" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="R44" s="5">
-        <v>35</v>
-      </c>
-      <c r="S44" s="5">
-        <v>2058</v>
-      </c>
-      <c r="T44" s="5">
-        <v>2200</v>
-      </c>
-      <c r="U44" s="5">
-        <v>24</v>
-      </c>
-      <c r="V44" s="5">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="45" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F45" s="2"/>
-      <c r="J45" s="5">
-        <v>36</v>
-      </c>
-      <c r="K45" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L45" s="5">
-        <v>2194</v>
-      </c>
-      <c r="M45" s="5">
-        <v>14</v>
-      </c>
-      <c r="N45" s="5">
-        <v>820</v>
-      </c>
-      <c r="O45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q45" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="R45" s="5">
-        <v>36</v>
-      </c>
-      <c r="S45" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T45" s="5">
-        <v>2194</v>
-      </c>
-      <c r="U45" s="5">
-        <v>14</v>
-      </c>
-      <c r="V45" s="5">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="46" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F46" s="2"/>
-      <c r="J46" s="5">
-        <v>37</v>
-      </c>
-      <c r="K46" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L46" s="5">
-        <v>2224</v>
-      </c>
-      <c r="M46" s="5">
-        <v>14</v>
-      </c>
-      <c r="N46" s="5">
-        <v>782</v>
-      </c>
-      <c r="O46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="R46" s="5">
-        <v>37</v>
-      </c>
-      <c r="S46" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T46" s="5">
-        <v>2224</v>
-      </c>
-      <c r="U46" s="5">
-        <v>14</v>
-      </c>
-      <c r="V46" s="5">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="47" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F47" s="2"/>
-      <c r="J47" s="5">
-        <v>38</v>
-      </c>
-      <c r="K47" s="5">
-        <v>2057</v>
-      </c>
-      <c r="L47" s="5">
-        <v>2210</v>
-      </c>
-      <c r="M47" s="5">
-        <v>10</v>
-      </c>
-      <c r="N47" s="5">
-        <v>914</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q47" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="R47" s="5">
-        <v>38</v>
-      </c>
-      <c r="S47" s="5">
-        <v>2057</v>
-      </c>
-      <c r="T47" s="5">
-        <v>2210</v>
-      </c>
-      <c r="U47" s="5">
-        <v>10</v>
-      </c>
-      <c r="V47" s="5">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="48" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F48" s="2"/>
-      <c r="J48" s="5">
-        <v>39</v>
-      </c>
-      <c r="K48" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L48" s="5">
-        <v>2220</v>
-      </c>
-      <c r="M48" s="5">
-        <v>10</v>
-      </c>
-      <c r="N48" s="5">
-        <v>1018</v>
-      </c>
-      <c r="O48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="R48" s="5">
-        <v>39</v>
-      </c>
-      <c r="S48" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T48" s="5">
-        <v>2220</v>
-      </c>
-      <c r="U48" s="5">
-        <v>10</v>
-      </c>
-      <c r="V48" s="5">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="49" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F49" s="2"/>
-      <c r="J49" s="5">
-        <v>40</v>
-      </c>
-      <c r="K49" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L49" s="5">
-        <v>2250</v>
-      </c>
-      <c r="M49" s="5">
-        <v>9</v>
-      </c>
-      <c r="N49" s="5">
-        <v>806</v>
-      </c>
-      <c r="O49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q49" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="R49" s="5">
-        <v>40</v>
-      </c>
-      <c r="S49" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T49" s="5">
-        <v>2250</v>
-      </c>
-      <c r="U49" s="5">
-        <v>9</v>
-      </c>
-      <c r="V49" s="5">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="50" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F50" s="2"/>
-      <c r="J50" s="5">
-        <v>41</v>
-      </c>
-      <c r="K50" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L50" s="5">
-        <v>2214</v>
-      </c>
-      <c r="M50" s="5">
-        <v>9</v>
-      </c>
-      <c r="N50" s="5">
-        <v>673</v>
-      </c>
-      <c r="O50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q50" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="R50" s="5">
-        <v>41</v>
-      </c>
-      <c r="S50" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T50" s="5">
-        <v>2214</v>
-      </c>
-      <c r="U50" s="5">
-        <v>9</v>
-      </c>
-      <c r="V50" s="5">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="51" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F51" s="2"/>
-      <c r="J51" s="5">
-        <v>42</v>
-      </c>
-      <c r="K51" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L51" s="5">
-        <v>2205</v>
-      </c>
-      <c r="M51" s="5">
-        <v>9</v>
-      </c>
-      <c r="N51" s="5">
-        <v>660</v>
-      </c>
-      <c r="O51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q51" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="R51" s="5">
-        <v>42</v>
-      </c>
-      <c r="S51" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T51" s="5">
-        <v>2205</v>
-      </c>
-      <c r="U51" s="5">
-        <v>9</v>
-      </c>
-      <c r="V51" s="5">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="52" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F52" s="2"/>
-      <c r="J52" s="5">
-        <v>43</v>
-      </c>
-      <c r="K52" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L52" s="5">
-        <v>2220</v>
-      </c>
-      <c r="M52" s="5">
-        <v>358</v>
-      </c>
-      <c r="N52" s="5">
-        <v>647</v>
-      </c>
-      <c r="O52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q52" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="R52" s="5">
-        <v>43</v>
-      </c>
-      <c r="S52" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T52" s="5">
-        <v>2220</v>
-      </c>
-      <c r="U52" s="5">
-        <v>358</v>
-      </c>
-      <c r="V52" s="5">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="53" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F53" s="2"/>
-      <c r="J53" s="5">
-        <v>44</v>
-      </c>
-      <c r="K53" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L53" s="5">
-        <v>2202</v>
-      </c>
-      <c r="M53" s="5">
-        <v>438</v>
-      </c>
-      <c r="N53" s="5">
-        <v>649</v>
-      </c>
-      <c r="O53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q53" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="R53" s="5">
-        <v>44</v>
-      </c>
-      <c r="S53" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T53" s="5">
-        <v>2202</v>
-      </c>
-      <c r="U53" s="5">
-        <v>438</v>
-      </c>
-      <c r="V53" s="5">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="54" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F54" s="2"/>
-      <c r="J54" s="5">
-        <v>45</v>
-      </c>
-      <c r="K54" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L54" s="5">
-        <v>2186</v>
-      </c>
-      <c r="M54" s="5">
-        <v>454</v>
-      </c>
-      <c r="N54" s="5">
-        <v>652</v>
-      </c>
-      <c r="O54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="R54" s="5">
-        <v>45</v>
-      </c>
-      <c r="S54" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T54" s="5">
-        <v>2186</v>
-      </c>
-      <c r="U54" s="5">
-        <v>454</v>
-      </c>
-      <c r="V54" s="5">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="55" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F55" s="2"/>
-      <c r="J55" s="5">
-        <v>46</v>
-      </c>
-      <c r="K55" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L55" s="5">
-        <v>2220</v>
-      </c>
-      <c r="M55" s="5">
-        <v>443</v>
-      </c>
-      <c r="N55" s="5">
-        <v>682</v>
-      </c>
-      <c r="O55" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q55" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="R55" s="5">
-        <v>46</v>
-      </c>
-      <c r="S55" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T55" s="5">
-        <v>2220</v>
-      </c>
-      <c r="U55" s="5">
-        <v>443</v>
-      </c>
-      <c r="V55" s="5">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="56" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F56" s="2"/>
-      <c r="J56" s="5">
-        <v>47</v>
-      </c>
-      <c r="K56" s="5">
-        <v>2060</v>
-      </c>
-      <c r="L56" s="5">
-        <v>2226</v>
-      </c>
-      <c r="M56" s="5">
-        <v>444</v>
-      </c>
-      <c r="N56" s="5">
-        <v>702</v>
-      </c>
-      <c r="O56" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q56" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="R56" s="5">
-        <v>47</v>
-      </c>
-      <c r="S56" s="5">
-        <v>2060</v>
-      </c>
-      <c r="T56" s="5">
-        <v>2226</v>
-      </c>
-      <c r="U56" s="5">
-        <v>444</v>
-      </c>
-      <c r="V56" s="5">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="57" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F57" s="2"/>
-      <c r="J57" s="5">
-        <v>48</v>
-      </c>
-      <c r="K57" s="5">
-        <v>2063</v>
-      </c>
-      <c r="L57" s="5">
-        <v>2226</v>
-      </c>
-      <c r="M57" s="5">
-        <v>444</v>
-      </c>
-      <c r="N57" s="5">
-        <v>707</v>
-      </c>
-      <c r="O57" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q57" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R57" s="5">
-        <v>48</v>
-      </c>
-      <c r="S57" s="5">
-        <v>2063</v>
-      </c>
-      <c r="T57" s="5">
-        <v>2226</v>
-      </c>
-      <c r="U57" s="5">
-        <v>444</v>
-      </c>
-      <c r="V57" s="5">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="58" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F58" s="2"/>
-      <c r="J58" s="5">
-        <v>49</v>
-      </c>
-      <c r="K58" s="5">
-        <v>2062</v>
-      </c>
-      <c r="L58" s="5">
-        <v>2210</v>
-      </c>
-      <c r="M58" s="5">
-        <v>440</v>
-      </c>
-      <c r="N58" s="5">
-        <v>698</v>
-      </c>
-      <c r="O58" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q58" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="R58" s="5">
-        <v>49</v>
-      </c>
-      <c r="S58" s="5">
-        <v>2062</v>
-      </c>
-      <c r="T58" s="5">
-        <v>2210</v>
-      </c>
-      <c r="U58" s="5">
-        <v>440</v>
-      </c>
-      <c r="V58" s="5">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="59" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F59" s="2"/>
-      <c r="J59" s="5">
-        <v>50</v>
-      </c>
-      <c r="K59" s="5">
-        <v>2067</v>
-      </c>
-      <c r="L59" s="5">
-        <v>2217</v>
-      </c>
-      <c r="M59" s="5">
-        <v>437</v>
-      </c>
-      <c r="N59" s="5">
-        <v>692</v>
-      </c>
-      <c r="O59" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q59" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="R59" s="5">
-        <v>50</v>
-      </c>
-      <c r="S59" s="5">
-        <v>2067</v>
-      </c>
-      <c r="T59" s="5">
-        <v>2217</v>
-      </c>
-      <c r="U59" s="5">
-        <v>437</v>
-      </c>
-      <c r="V59" s="5">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="60" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F60" s="2"/>
-      <c r="J60" s="5">
-        <v>51</v>
-      </c>
-      <c r="K60" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L60" s="5">
-        <v>2217</v>
-      </c>
-      <c r="M60" s="5">
-        <v>428</v>
-      </c>
-      <c r="N60" s="5">
-        <v>690</v>
-      </c>
-      <c r="O60" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q60" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="R60" s="5">
-        <v>51</v>
-      </c>
-      <c r="S60" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T60" s="5">
-        <v>2217</v>
-      </c>
-      <c r="U60" s="5">
-        <v>428</v>
-      </c>
-      <c r="V60" s="5">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="61" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F61" s="2"/>
-      <c r="J61" s="5">
-        <v>52</v>
-      </c>
-      <c r="K61" s="5">
-        <v>2067</v>
-      </c>
-      <c r="L61" s="5">
-        <v>2223</v>
-      </c>
-      <c r="M61" s="5">
-        <v>418</v>
-      </c>
-      <c r="N61" s="5">
-        <v>700</v>
-      </c>
-      <c r="O61" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q61" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="R61" s="5">
-        <v>52</v>
-      </c>
-      <c r="S61" s="5">
-        <v>2067</v>
-      </c>
-      <c r="T61" s="5">
-        <v>2223</v>
-      </c>
-      <c r="U61" s="5">
-        <v>418</v>
-      </c>
-      <c r="V61" s="5">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="62" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F62" s="2"/>
-      <c r="J62" s="5">
-        <v>53</v>
-      </c>
-      <c r="K62" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L62" s="5">
-        <v>2222</v>
-      </c>
-      <c r="M62" s="5">
-        <v>418</v>
-      </c>
-      <c r="N62" s="5">
-        <v>708</v>
-      </c>
-      <c r="O62" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q62" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="R62" s="5">
-        <v>53</v>
-      </c>
-      <c r="S62" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T62" s="5">
-        <v>2222</v>
-      </c>
-      <c r="U62" s="5">
-        <v>418</v>
-      </c>
-      <c r="V62" s="5">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="63" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F63" s="2"/>
-      <c r="J63" s="5">
-        <v>54</v>
-      </c>
-      <c r="K63" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L63" s="5">
-        <v>2232</v>
-      </c>
-      <c r="M63" s="5">
-        <v>418</v>
-      </c>
-      <c r="N63" s="5">
-        <v>717</v>
-      </c>
-      <c r="O63" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q63" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="R63" s="5">
-        <v>54</v>
-      </c>
-      <c r="S63" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T63" s="5">
-        <v>2232</v>
-      </c>
-      <c r="U63" s="5">
-        <v>418</v>
-      </c>
-      <c r="V63" s="5">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="64" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F64" s="2"/>
-      <c r="J64" s="5">
-        <v>55</v>
-      </c>
-      <c r="K64" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L64" s="5">
-        <v>2236</v>
-      </c>
-      <c r="M64" s="5">
-        <v>429</v>
-      </c>
-      <c r="N64" s="5">
-        <v>723</v>
-      </c>
-      <c r="O64" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q64" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="R64" s="5">
-        <v>55</v>
-      </c>
-      <c r="S64" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T64" s="5">
-        <v>2236</v>
-      </c>
-      <c r="U64" s="5">
-        <v>429</v>
-      </c>
-      <c r="V64" s="5">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="65" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F65" s="2"/>
-      <c r="J65" s="5">
-        <v>56</v>
-      </c>
-      <c r="K65" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L65" s="5">
-        <v>2272</v>
-      </c>
-      <c r="M65" s="5">
-        <v>434</v>
-      </c>
-      <c r="N65" s="5">
-        <v>727</v>
-      </c>
-      <c r="O65" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q65" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="R65" s="5">
-        <v>56</v>
-      </c>
-      <c r="S65" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T65" s="5">
-        <v>2272</v>
-      </c>
-      <c r="U65" s="5">
-        <v>434</v>
-      </c>
-      <c r="V65" s="5">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="66" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F66" s="2"/>
-      <c r="J66" s="5">
-        <v>57</v>
-      </c>
-      <c r="K66" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L66" s="5">
-        <v>2252</v>
-      </c>
-      <c r="M66" s="5">
-        <v>434</v>
-      </c>
-      <c r="N66" s="5">
-        <v>736</v>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q66" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="R66" s="5">
-        <v>57</v>
-      </c>
-      <c r="S66" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T66" s="5">
-        <v>2252</v>
-      </c>
-      <c r="U66" s="5">
-        <v>434</v>
-      </c>
-      <c r="V66" s="5">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="67" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F67" s="2"/>
-      <c r="J67" s="5">
-        <v>58</v>
-      </c>
-      <c r="K67" s="5">
-        <v>2070</v>
-      </c>
-      <c r="L67" s="5">
-        <v>2270</v>
-      </c>
-      <c r="M67" s="5">
-        <v>424</v>
-      </c>
-      <c r="N67" s="5">
-        <v>734</v>
-      </c>
-      <c r="O67" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q67" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="R67" s="5">
-        <v>58</v>
-      </c>
-      <c r="S67" s="5">
-        <v>2070</v>
-      </c>
-      <c r="T67" s="5">
-        <v>2270</v>
-      </c>
-      <c r="U67" s="5">
-        <v>424</v>
-      </c>
-      <c r="V67" s="5">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="68" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F68" s="2"/>
-      <c r="J68" s="5">
-        <v>59</v>
-      </c>
-      <c r="K68" s="5">
-        <v>2074</v>
-      </c>
-      <c r="L68" s="5">
-        <v>2262</v>
-      </c>
-      <c r="M68" s="5">
-        <v>438</v>
-      </c>
-      <c r="N68" s="5">
-        <v>734</v>
-      </c>
-      <c r="O68" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q68" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="R68" s="5">
-        <v>59</v>
-      </c>
-      <c r="S68" s="5">
-        <v>2074</v>
-      </c>
-      <c r="T68" s="5">
-        <v>2262</v>
-      </c>
-      <c r="U68" s="5">
-        <v>438</v>
-      </c>
-      <c r="V68" s="5">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="69" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F69" s="2"/>
-      <c r="J69" s="5">
-        <v>60</v>
-      </c>
-      <c r="K69" s="5">
-        <v>2074</v>
-      </c>
-      <c r="L69" s="5">
-        <v>2265</v>
-      </c>
-      <c r="M69" s="5">
-        <v>428</v>
-      </c>
-      <c r="N69" s="5">
-        <v>732</v>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q69" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R69" s="5">
-        <v>60</v>
-      </c>
-      <c r="S69" s="5">
-        <v>2074</v>
-      </c>
-      <c r="T69" s="5">
-        <v>2265</v>
-      </c>
-      <c r="U69" s="5">
-        <v>428</v>
-      </c>
-      <c r="V69" s="5">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="70" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F70" s="2"/>
-      <c r="J70" s="5">
-        <v>61</v>
-      </c>
-      <c r="K70" s="5">
-        <v>2079</v>
-      </c>
-      <c r="L70" s="5">
-        <v>2260</v>
-      </c>
-      <c r="M70" s="5">
-        <v>438</v>
-      </c>
-      <c r="N70" s="5">
-        <v>732</v>
-      </c>
-      <c r="O70" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q70" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="R70" s="5">
-        <v>61</v>
-      </c>
-      <c r="S70" s="5">
-        <v>2079</v>
-      </c>
-      <c r="T70" s="5">
-        <v>2260</v>
-      </c>
-      <c r="U70" s="5">
-        <v>438</v>
-      </c>
-      <c r="V70" s="5">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="71" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F71" s="2"/>
-      <c r="J71" s="5">
-        <v>62</v>
-      </c>
-      <c r="K71" s="5">
-        <v>2086</v>
-      </c>
-      <c r="L71" s="5">
-        <v>2273</v>
-      </c>
-      <c r="M71" s="5">
-        <v>443</v>
-      </c>
-      <c r="N71" s="5">
-        <v>736</v>
-      </c>
-      <c r="O71" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q71" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="R71" s="5">
-        <v>62</v>
-      </c>
-      <c r="S71" s="5">
-        <v>2086</v>
-      </c>
-      <c r="T71" s="5">
-        <v>2273</v>
-      </c>
-      <c r="U71" s="5">
-        <v>443</v>
-      </c>
-      <c r="V71" s="5">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="72" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F72" s="2"/>
-      <c r="J72" s="5">
-        <v>63</v>
-      </c>
-      <c r="K72" s="5">
-        <v>2089</v>
-      </c>
-      <c r="L72" s="5">
-        <v>2262</v>
-      </c>
-      <c r="M72" s="5">
-        <v>447</v>
-      </c>
-      <c r="N72" s="5">
-        <v>726</v>
-      </c>
-      <c r="O72" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q72" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="R72" s="5">
-        <v>63</v>
-      </c>
-      <c r="S72" s="5">
-        <v>2089</v>
-      </c>
-      <c r="T72" s="5">
-        <v>2262</v>
-      </c>
-      <c r="U72" s="5">
-        <v>447</v>
-      </c>
-      <c r="V72" s="5">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="73" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F73" s="2"/>
-      <c r="J73" s="5">
-        <v>64</v>
-      </c>
-      <c r="K73" s="5">
-        <v>2092</v>
-      </c>
-      <c r="L73" s="5">
-        <v>2265</v>
-      </c>
-      <c r="M73" s="5">
-        <v>444</v>
-      </c>
-      <c r="N73" s="5">
-        <v>732</v>
-      </c>
-      <c r="O73" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q73" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="R73" s="5">
-        <v>64</v>
-      </c>
-      <c r="S73" s="5">
-        <v>2092</v>
-      </c>
-      <c r="T73" s="5">
-        <v>2265</v>
-      </c>
-      <c r="U73" s="5">
-        <v>444</v>
-      </c>
-      <c r="V73" s="5">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="74" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F74" s="2"/>
-      <c r="J74" s="5">
-        <v>65</v>
-      </c>
-      <c r="K74" s="5">
-        <v>2100</v>
-      </c>
-      <c r="L74" s="5">
-        <v>2270</v>
-      </c>
-      <c r="M74" s="5">
-        <v>447</v>
-      </c>
-      <c r="N74" s="5">
-        <v>735</v>
-      </c>
-      <c r="O74" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q74" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="R74" s="5">
-        <v>65</v>
-      </c>
-      <c r="S74" s="5">
-        <v>2100</v>
-      </c>
-      <c r="T74" s="5">
-        <v>2270</v>
-      </c>
-      <c r="U74" s="5">
-        <v>447</v>
-      </c>
-      <c r="V74" s="5">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="75" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F75" s="2"/>
-      <c r="J75" s="5">
-        <v>66</v>
-      </c>
-      <c r="K75" s="5">
-        <v>2100</v>
-      </c>
-      <c r="L75" s="5">
-        <v>2282</v>
-      </c>
-      <c r="M75" s="5">
+    <row r="77" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G77" s="2" t="b" cm="1">
+        <f t="array" ref="G77">AND(K77:N77=S77:V77)</f>
+        <v>1</v>
+      </c>
+      <c r="J77" s="3">
+        <v>68</v>
+      </c>
+      <c r="K77" s="3">
+        <v>2110</v>
+      </c>
+      <c r="L77" s="3">
+        <v>2323</v>
+      </c>
+      <c r="M77" s="3">
         <v>450</v>
       </c>
-      <c r="N75" s="5">
-        <v>736</v>
-      </c>
-      <c r="O75" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q75" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="R75" s="5">
-        <v>66</v>
-      </c>
-      <c r="S75" s="5">
-        <v>2100</v>
-      </c>
-      <c r="T75" s="5">
-        <v>2282</v>
-      </c>
-      <c r="U75" s="5">
+      <c r="N77" s="3">
+        <v>828</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q77" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="R77" s="3">
+        <v>68</v>
+      </c>
+      <c r="S77" s="3">
+        <v>2110</v>
+      </c>
+      <c r="T77" s="3">
+        <v>2323</v>
+      </c>
+      <c r="U77" s="3">
         <v>450</v>
       </c>
-      <c r="V75" s="5">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="76" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F76" s="2"/>
-      <c r="J76" s="5">
-        <v>67</v>
-      </c>
-      <c r="K76" s="5">
-        <v>2105</v>
-      </c>
-      <c r="L76" s="5">
-        <v>2329</v>
-      </c>
-      <c r="M76" s="5">
-        <v>436</v>
-      </c>
-      <c r="N76" s="5">
-        <v>812</v>
-      </c>
-      <c r="O76" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q76" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="R76" s="5">
-        <v>67</v>
-      </c>
-      <c r="S76" s="5">
-        <v>2105</v>
-      </c>
-      <c r="T76" s="5">
-        <v>2329</v>
-      </c>
-      <c r="U76" s="5">
-        <v>436</v>
-      </c>
-      <c r="V76" s="5">
-        <v>812</v>
-      </c>
-      <c r="Y76" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z76" s="7"/>
-      <c r="AA76" s="7"/>
-      <c r="AB76" s="7"/>
-      <c r="AC76" s="7"/>
-      <c r="AD76" s="7"/>
-      <c r="AE76" s="7"/>
-      <c r="AF76" s="7"/>
-      <c r="AG76" s="6"/>
-    </row>
-    <row r="77" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F77" s="2"/>
-      <c r="J77" s="5">
-        <v>68</v>
-      </c>
-      <c r="K77" s="5">
-        <v>2110</v>
-      </c>
-      <c r="L77" s="5">
-        <v>2323</v>
-      </c>
-      <c r="M77" s="5">
-        <v>450</v>
-      </c>
-      <c r="N77" s="5">
+      <c r="V77" s="3">
         <v>828</v>
       </c>
-      <c r="O77" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q77" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="R77" s="5">
-        <v>68</v>
-      </c>
-      <c r="S77" s="5">
-        <v>2110</v>
-      </c>
-      <c r="T77" s="5">
-        <v>2323</v>
-      </c>
-      <c r="U77" s="5">
-        <v>450</v>
-      </c>
-      <c r="V77" s="5">
-        <v>828</v>
-      </c>
-      <c r="Y77" s="3" t="s">
+      <c r="W77" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999999566935003</v>
+      </c>
+      <c r="Y77" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="Z77" s="3"/>
-      <c r="AA77" s="3"/>
-      <c r="AB77" s="3"/>
-      <c r="AC77" s="3">
+      <c r="Z77" s="8"/>
+      <c r="AA77" s="8"/>
+      <c r="AB77" s="8"/>
+      <c r="AC77" s="8">
         <f>90/Q100</f>
         <v>1.6853459172495155E-2</v>
       </c>
-      <c r="AD77" s="3"/>
-      <c r="AE77" s="3"/>
-      <c r="AF77" s="3"/>
+      <c r="AD77" s="8"/>
+      <c r="AE77" s="8"/>
+      <c r="AF77" s="8"/>
     </row>
-    <row r="78" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F78" s="2"/>
-      <c r="J78" s="5">
+    <row r="78" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G78" s="2" t="b" cm="1">
+        <f t="array" ref="G78">AND(K78:N78=S78:V78)</f>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3">
         <v>69</v>
       </c>
-      <c r="K78" s="5">
+      <c r="K78" s="3">
         <v>2120</v>
       </c>
-      <c r="L78" s="5">
+      <c r="L78" s="3">
         <v>2310</v>
       </c>
-      <c r="M78" s="5">
+      <c r="M78" s="3">
         <v>442</v>
       </c>
-      <c r="N78" s="5">
+      <c r="N78" s="3">
         <v>776</v>
       </c>
-      <c r="O78" s="5" t="s">
+      <c r="O78" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Q78" s="5" t="s">
+      <c r="Q78" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="R78" s="5">
+      <c r="R78" s="3">
         <v>69</v>
       </c>
-      <c r="S78" s="5">
+      <c r="S78" s="3">
         <v>2120</v>
       </c>
-      <c r="T78" s="5">
+      <c r="T78" s="3">
         <v>2310</v>
       </c>
-      <c r="U78" s="5">
+      <c r="U78" s="3">
         <v>442</v>
       </c>
-      <c r="V78" s="5">
+      <c r="V78" s="3">
         <v>776</v>
       </c>
+      <c r="W78" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="79" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F79" s="2"/>
-      <c r="J79" s="5">
+    <row r="79" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G79" s="2" t="b" cm="1">
+        <f t="array" ref="G79">AND(K79:N79=S79:V79)</f>
+        <v>1</v>
+      </c>
+      <c r="J79" s="3">
         <v>70</v>
       </c>
-      <c r="K79" s="5">
+      <c r="K79" s="3">
         <v>2115</v>
       </c>
-      <c r="L79" s="5">
+      <c r="L79" s="3">
         <v>2324</v>
       </c>
-      <c r="M79" s="5">
+      <c r="M79" s="3">
         <v>455</v>
       </c>
-      <c r="N79" s="5">
+      <c r="N79" s="3">
         <v>787</v>
       </c>
-      <c r="O79" s="5" t="s">
+      <c r="O79" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Q79" s="5" t="s">
+      <c r="Q79" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="R79" s="5">
+      <c r="R79" s="3">
         <v>70</v>
       </c>
-      <c r="S79" s="5">
+      <c r="S79" s="3">
         <v>2115</v>
       </c>
-      <c r="T79" s="5">
+      <c r="T79" s="3">
         <v>2324</v>
       </c>
-      <c r="U79" s="5">
+      <c r="U79" s="3">
         <v>455</v>
       </c>
-      <c r="V79" s="5">
+      <c r="V79" s="3">
         <v>787</v>
       </c>
+      <c r="W79" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="80" spans="6:33" x14ac:dyDescent="0.25">
-      <c r="F80" s="2"/>
-      <c r="J80" s="5">
+    <row r="80" spans="7:33" x14ac:dyDescent="0.25">
+      <c r="G80" s="2" t="b" cm="1">
+        <f t="array" ref="G80">AND(K80:N80=S80:V80)</f>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3">
         <v>71</v>
       </c>
-      <c r="K80" s="5">
+      <c r="K80" s="3">
         <v>2120</v>
       </c>
-      <c r="L80" s="5">
+      <c r="L80" s="3">
         <v>2347</v>
       </c>
-      <c r="M80" s="5">
+      <c r="M80" s="3">
         <v>444</v>
       </c>
-      <c r="N80" s="5">
+      <c r="N80" s="3">
         <v>818</v>
       </c>
-      <c r="O80" s="5" t="s">
+      <c r="O80" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="Q80" s="5" t="s">
+      <c r="Q80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="R80" s="5">
+      <c r="R80" s="3">
         <v>71</v>
       </c>
-      <c r="S80" s="5">
+      <c r="S80" s="3">
         <v>2120</v>
       </c>
-      <c r="T80" s="5">
+      <c r="T80" s="3">
         <v>2347</v>
       </c>
-      <c r="U80" s="5">
+      <c r="U80" s="3">
         <v>444</v>
       </c>
-      <c r="V80" s="5">
+      <c r="V80" s="3">
         <v>818</v>
       </c>
+      <c r="W80" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000999737530947</v>
+      </c>
     </row>
-    <row r="81" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F81" s="2"/>
-      <c r="J81" s="5">
+    <row r="81" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G81" s="2" t="b" cm="1">
+        <f t="array" ref="G81">AND(K81:N81=S81:V81)</f>
+        <v>1</v>
+      </c>
+      <c r="J81" s="3">
         <v>72</v>
       </c>
-      <c r="K81" s="5">
+      <c r="K81" s="3">
         <v>2124</v>
       </c>
-      <c r="L81" s="5">
+      <c r="L81" s="3">
         <v>2355</v>
       </c>
-      <c r="M81" s="5">
+      <c r="M81" s="3">
         <v>460</v>
       </c>
-      <c r="N81" s="5">
+      <c r="N81" s="3">
         <v>844</v>
       </c>
-      <c r="O81" s="5" t="s">
+      <c r="O81" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Q81" s="5" t="s">
+      <c r="Q81" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="R81" s="5">
+      <c r="R81" s="3">
         <v>72</v>
       </c>
-      <c r="S81" s="5">
+      <c r="S81" s="3">
         <v>2124</v>
       </c>
-      <c r="T81" s="5">
+      <c r="T81" s="3">
         <v>2355</v>
       </c>
-      <c r="U81" s="5">
+      <c r="U81" s="3">
         <v>460</v>
       </c>
-      <c r="V81" s="5">
+      <c r="V81" s="3">
         <v>844</v>
       </c>
+      <c r="W81" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="82" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F82" s="2"/>
-      <c r="J82" s="5">
+    <row r="82" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G82" s="2" t="b" cm="1">
+        <f t="array" ref="G82">AND(K82:N82=S82:V82)</f>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3">
         <v>73</v>
       </c>
-      <c r="K82" s="5">
+      <c r="K82" s="3">
         <v>2127</v>
       </c>
-      <c r="L82" s="5">
+      <c r="L82" s="3">
         <v>2368</v>
       </c>
-      <c r="M82" s="5">
+      <c r="M82" s="3">
         <v>458</v>
       </c>
-      <c r="N82" s="5">
+      <c r="N82" s="3">
         <v>858</v>
       </c>
-      <c r="O82" s="5" t="s">
+      <c r="O82" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="Q82" s="5" t="s">
+      <c r="Q82" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="R82" s="5">
+      <c r="R82" s="3">
         <v>73</v>
       </c>
-      <c r="S82" s="5">
+      <c r="S82" s="3">
         <v>2127</v>
       </c>
-      <c r="T82" s="5">
+      <c r="T82" s="3">
         <v>2368</v>
       </c>
-      <c r="U82" s="5">
+      <c r="U82" s="3">
         <v>458</v>
       </c>
-      <c r="V82" s="5">
+      <c r="V82" s="3">
         <v>858</v>
       </c>
+      <c r="W82" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999999566935003</v>
+      </c>
     </row>
-    <row r="83" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F83" s="2"/>
-      <c r="J83" s="5">
+    <row r="83" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G83" s="2" t="b" cm="1">
+        <f t="array" ref="G83">AND(K83:N83=S83:V83)</f>
+        <v>1</v>
+      </c>
+      <c r="J83" s="3">
         <v>74</v>
       </c>
-      <c r="K83" s="5">
+      <c r="K83" s="3">
         <v>2134</v>
       </c>
-      <c r="L83" s="5">
+      <c r="L83" s="3">
         <v>2374</v>
       </c>
-      <c r="M83" s="5">
+      <c r="M83" s="3">
         <v>460</v>
       </c>
-      <c r="N83" s="5">
+      <c r="N83" s="3">
         <v>892</v>
       </c>
-      <c r="O83" s="5" t="s">
+      <c r="O83" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q83" s="5" t="s">
+      <c r="Q83" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="R83" s="5">
+      <c r="R83" s="3">
         <v>74</v>
       </c>
-      <c r="S83" s="5">
+      <c r="S83" s="3">
         <v>2134</v>
       </c>
-      <c r="T83" s="5">
+      <c r="T83" s="3">
         <v>2374</v>
       </c>
-      <c r="U83" s="5">
+      <c r="U83" s="3">
         <v>460</v>
       </c>
-      <c r="V83" s="5">
+      <c r="V83" s="3">
         <v>892</v>
       </c>
+      <c r="W83" s="1">
+        <f t="shared" si="1"/>
+        <v>60.001000366173685</v>
+      </c>
     </row>
-    <row r="84" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F84" s="2"/>
-      <c r="J84" s="5">
+    <row r="84" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G84" s="2" t="b" cm="1">
+        <f t="array" ref="G84">AND(K84:N84=S84:V84)</f>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3">
         <v>75</v>
       </c>
-      <c r="K84" s="5">
+      <c r="K84" s="3">
         <v>2134</v>
       </c>
-      <c r="L84" s="5">
+      <c r="L84" s="3">
         <v>2379</v>
       </c>
-      <c r="M84" s="5">
+      <c r="M84" s="3">
         <v>470</v>
       </c>
-      <c r="N84" s="5">
+      <c r="N84" s="3">
         <v>902</v>
       </c>
-      <c r="O84" s="5" t="s">
+      <c r="O84" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Q84" s="5" t="s">
+      <c r="Q84" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="R84" s="5">
+      <c r="R84" s="3">
         <v>75</v>
       </c>
-      <c r="S84" s="5">
+      <c r="S84" s="3">
         <v>2134</v>
       </c>
-      <c r="T84" s="5">
+      <c r="T84" s="3">
         <v>2379</v>
       </c>
-      <c r="U84" s="5">
+      <c r="U84" s="3">
         <v>470</v>
       </c>
-      <c r="V84" s="5">
+      <c r="V84" s="3">
         <v>902</v>
       </c>
+      <c r="W84" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="85" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F85" s="2"/>
-      <c r="J85" s="5">
+    <row r="85" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G85" s="2" t="b" cm="1">
+        <f t="array" ref="G85">AND(K85:N85=S85:V85)</f>
+        <v>1</v>
+      </c>
+      <c r="J85" s="3">
         <v>76</v>
       </c>
-      <c r="K85" s="5">
+      <c r="K85" s="3">
         <v>2139</v>
       </c>
-      <c r="L85" s="5">
+      <c r="L85" s="3">
         <v>2389</v>
       </c>
-      <c r="M85" s="5">
+      <c r="M85" s="3">
         <v>475</v>
       </c>
-      <c r="N85" s="5">
+      <c r="N85" s="3">
         <v>878</v>
       </c>
-      <c r="O85" s="5" t="s">
+      <c r="O85" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Q85" s="5" t="s">
+      <c r="Q85" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="R85" s="5">
+      <c r="R85" s="3">
         <v>76</v>
       </c>
-      <c r="S85" s="5">
+      <c r="S85" s="3">
         <v>2139</v>
       </c>
-      <c r="T85" s="5">
+      <c r="T85" s="3">
         <v>2389</v>
       </c>
-      <c r="U85" s="5">
+      <c r="U85" s="3">
         <v>475</v>
       </c>
-      <c r="V85" s="5">
+      <c r="V85" s="3">
         <v>878</v>
       </c>
+      <c r="W85" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999999566935003</v>
+      </c>
     </row>
-    <row r="86" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F86" s="2"/>
-      <c r="J86" s="5">
+    <row r="86" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G86" s="2" t="b" cm="1">
+        <f t="array" ref="G86">AND(K86:N86=S86:V86)</f>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3">
         <v>77</v>
       </c>
-      <c r="K86" s="5">
+      <c r="K86" s="3">
         <v>2142</v>
       </c>
-      <c r="L86" s="5">
+      <c r="L86" s="3">
         <v>2397</v>
       </c>
-      <c r="M86" s="5">
+      <c r="M86" s="3">
         <v>472</v>
       </c>
-      <c r="N86" s="5">
+      <c r="N86" s="3">
         <v>869</v>
       </c>
-      <c r="O86" s="5" t="s">
+      <c r="O86" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Q86" s="5" t="s">
+      <c r="Q86" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="R86" s="5">
+      <c r="R86" s="3">
         <v>77</v>
       </c>
-      <c r="S86" s="5">
+      <c r="S86" s="3">
         <v>2142</v>
       </c>
-      <c r="T86" s="5">
+      <c r="T86" s="3">
         <v>2397</v>
       </c>
-      <c r="U86" s="5">
+      <c r="U86" s="3">
         <v>472</v>
       </c>
-      <c r="V86" s="5">
+      <c r="V86" s="3">
         <v>869</v>
       </c>
+      <c r="W86" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="87" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F87" s="2"/>
-      <c r="J87" s="5">
+    <row r="87" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G87" s="2" t="b" cm="1">
+        <f t="array" ref="G87">AND(K87:N87=S87:V87)</f>
+        <v>1</v>
+      </c>
+      <c r="J87" s="3">
         <v>78</v>
       </c>
-      <c r="K87" s="5">
+      <c r="K87" s="3">
         <v>2144</v>
       </c>
-      <c r="L87" s="5">
+      <c r="L87" s="3">
         <v>2405</v>
       </c>
-      <c r="M87" s="5">
+      <c r="M87" s="3">
         <v>466</v>
       </c>
-      <c r="N87" s="5">
+      <c r="N87" s="3">
         <v>868</v>
       </c>
-      <c r="O87" s="5" t="s">
+      <c r="O87" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Q87" s="5" t="s">
+      <c r="Q87" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="R87" s="5">
+      <c r="R87" s="3">
         <v>78</v>
       </c>
-      <c r="S87" s="5">
+      <c r="S87" s="3">
         <v>2144</v>
       </c>
-      <c r="T87" s="5">
+      <c r="T87" s="3">
         <v>2405</v>
       </c>
-      <c r="U87" s="5">
+      <c r="U87" s="3">
         <v>466</v>
       </c>
-      <c r="V87" s="5">
+      <c r="V87" s="3">
         <v>868</v>
       </c>
+      <c r="W87" s="1">
+        <f t="shared" si="1"/>
+        <v>60.030999826267362</v>
+      </c>
     </row>
-    <row r="88" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F88" s="2"/>
-      <c r="J88" s="5">
+    <row r="88" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G88" s="2" t="b" cm="1">
+        <f t="array" ref="G88">AND(K88:N88=S88:V88)</f>
+        <v>1</v>
+      </c>
+      <c r="J88" s="3">
         <v>79</v>
       </c>
-      <c r="K88" s="5">
+      <c r="K88" s="3">
         <v>2150</v>
       </c>
-      <c r="L88" s="5">
+      <c r="L88" s="3">
         <v>2410</v>
       </c>
-      <c r="M88" s="5">
+      <c r="M88" s="3">
         <v>476</v>
       </c>
-      <c r="N88" s="5">
+      <c r="N88" s="3">
         <v>903</v>
       </c>
-      <c r="O88" s="5" t="s">
+      <c r="O88" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q88" s="5" t="s">
+      <c r="Q88" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="R88" s="5">
+      <c r="R88" s="3">
         <v>79</v>
       </c>
-      <c r="S88" s="5">
+      <c r="S88" s="3">
         <v>2150</v>
       </c>
-      <c r="T88" s="5">
+      <c r="T88" s="3">
         <v>2410</v>
       </c>
-      <c r="U88" s="5">
+      <c r="U88" s="3">
         <v>476</v>
       </c>
-      <c r="V88" s="5">
+      <c r="V88" s="3">
         <v>903</v>
       </c>
+      <c r="W88" s="1">
+        <f t="shared" si="1"/>
+        <v>60.001000366173685</v>
+      </c>
     </row>
-    <row r="89" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F89" s="2"/>
-      <c r="J89" s="5">
+    <row r="89" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G89" s="2" t="b" cm="1">
+        <f t="array" ref="G89">AND(K89:N89=S89:V89)</f>
+        <v>1</v>
+      </c>
+      <c r="J89" s="3">
         <v>80</v>
       </c>
-      <c r="K89" s="5">
+      <c r="K89" s="3">
         <v>2155</v>
       </c>
-      <c r="L89" s="5">
+      <c r="L89" s="3">
         <v>2420</v>
       </c>
-      <c r="M89" s="5">
+      <c r="M89" s="3">
         <v>474</v>
       </c>
-      <c r="N89" s="5">
+      <c r="N89" s="3">
         <v>928</v>
       </c>
-      <c r="O89" s="5" t="s">
+      <c r="O89" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q89" s="5" t="s">
+      <c r="Q89" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="R89" s="5">
+      <c r="R89" s="3">
         <v>80</v>
       </c>
-      <c r="S89" s="5">
+      <c r="S89" s="3">
         <v>2155</v>
       </c>
-      <c r="T89" s="5">
+      <c r="T89" s="3">
         <v>2420</v>
       </c>
-      <c r="U89" s="5">
+      <c r="U89" s="3">
         <v>474</v>
       </c>
-      <c r="V89" s="5">
+      <c r="V89" s="3">
         <v>928</v>
       </c>
+      <c r="W89" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999000024981797</v>
+      </c>
     </row>
-    <row r="90" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F90" s="2"/>
-      <c r="J90" s="5">
+    <row r="90" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G90" s="2" t="b" cm="1">
+        <f t="array" ref="G90">AND(K90:N90=S90:V90)</f>
+        <v>1</v>
+      </c>
+      <c r="J90" s="3">
         <v>81</v>
       </c>
-      <c r="K90" s="5">
+      <c r="K90" s="3">
         <v>2158</v>
       </c>
-      <c r="L90" s="5">
+      <c r="L90" s="3">
         <v>2420</v>
       </c>
-      <c r="M90" s="5">
+      <c r="M90" s="3">
         <v>494</v>
       </c>
-      <c r="N90" s="5">
+      <c r="N90" s="3">
         <v>939</v>
       </c>
-      <c r="O90" s="5" t="s">
+      <c r="O90" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="Q90" s="5" t="s">
+      <c r="Q90" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="R90" s="5">
+      <c r="R90" s="3">
         <v>81</v>
       </c>
-      <c r="S90" s="5">
+      <c r="S90" s="3">
         <v>2158</v>
       </c>
-      <c r="T90" s="5">
+      <c r="T90" s="3">
         <v>2420</v>
       </c>
-      <c r="U90" s="5">
+      <c r="U90" s="3">
         <v>494</v>
       </c>
-      <c r="V90" s="5">
+      <c r="V90" s="3">
         <v>939</v>
       </c>
+      <c r="W90" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000999737530947</v>
+      </c>
     </row>
-    <row r="91" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F91" s="2"/>
-      <c r="J91" s="5">
+    <row r="91" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G91" s="2" t="b" cm="1">
+        <f t="array" ref="G91">AND(K91:N91=S91:V91)</f>
+        <v>1</v>
+      </c>
+      <c r="J91" s="3">
         <v>82</v>
       </c>
-      <c r="K91" s="5">
+      <c r="K91" s="3">
         <v>2162</v>
       </c>
-      <c r="L91" s="5">
+      <c r="L91" s="3">
         <v>2429</v>
       </c>
-      <c r="M91" s="5">
+      <c r="M91" s="3">
         <v>481</v>
       </c>
-      <c r="N91" s="5">
+      <c r="N91" s="3">
         <v>948</v>
       </c>
-      <c r="O91" s="5" t="s">
+      <c r="O91" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="Q91" s="5" t="s">
+      <c r="Q91" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="R91" s="5">
+      <c r="R91" s="3">
         <v>82</v>
       </c>
-      <c r="S91" s="5">
+      <c r="S91" s="3">
         <v>2162</v>
       </c>
-      <c r="T91" s="5">
+      <c r="T91" s="3">
         <v>2429</v>
       </c>
-      <c r="U91" s="5">
+      <c r="U91" s="3">
         <v>481</v>
       </c>
-      <c r="V91" s="5">
+      <c r="V91" s="3">
         <v>948</v>
       </c>
+      <c r="W91" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="92" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="F92" s="2"/>
-      <c r="J92" s="5">
+    <row r="92" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G92" s="2" t="b" cm="1">
+        <f t="array" ref="G92">AND(K92:N92=S92:V92)</f>
+        <v>1</v>
+      </c>
+      <c r="J92" s="3">
         <v>83</v>
       </c>
-      <c r="K92" s="5">
+      <c r="K92" s="3">
         <v>2170</v>
       </c>
-      <c r="L92" s="5">
+      <c r="L92" s="3">
         <v>2439</v>
       </c>
-      <c r="M92" s="5">
+      <c r="M92" s="3">
         <v>497</v>
       </c>
-      <c r="N92" s="5">
+      <c r="N92" s="3">
         <v>966</v>
       </c>
-      <c r="O92" s="5" t="s">
+      <c r="O92" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q92" s="5" t="s">
+      <c r="Q92" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="R92" s="5">
+      <c r="R92" s="3">
         <v>83</v>
       </c>
-      <c r="S92" s="5">
+      <c r="S92" s="3">
         <v>2170</v>
       </c>
-      <c r="T92" s="5">
+      <c r="T92" s="3">
         <v>2439</v>
       </c>
-      <c r="U92" s="5">
+      <c r="U92" s="3">
         <v>497</v>
       </c>
-      <c r="V92" s="5">
+      <c r="V92" s="3">
         <v>966</v>
       </c>
+      <c r="W92" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999999566935003</v>
+      </c>
     </row>
-    <row r="93" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="J93" s="5">
+    <row r="93" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G93" s="2" t="b" cm="1">
+        <f t="array" ref="G93">AND(K93:N93=S93:V93)</f>
+        <v>1</v>
+      </c>
+      <c r="J93" s="3">
         <v>84</v>
       </c>
-      <c r="K93" s="5">
+      <c r="K93" s="3">
         <v>2170</v>
       </c>
-      <c r="L93" s="5">
+      <c r="L93" s="3">
         <v>2439</v>
       </c>
-      <c r="M93" s="5">
+      <c r="M93" s="3">
         <v>494</v>
       </c>
-      <c r="N93" s="5">
+      <c r="N93" s="3">
         <v>965</v>
       </c>
-      <c r="O93" s="5" t="s">
+      <c r="O93" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Q93" s="5" t="s">
+      <c r="Q93" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="R93" s="5">
+      <c r="R93" s="3">
         <v>84</v>
       </c>
-      <c r="S93" s="5">
+      <c r="S93" s="3">
         <v>2170</v>
       </c>
-      <c r="T93" s="5">
+      <c r="T93" s="3">
         <v>2439</v>
       </c>
-      <c r="U93" s="5">
+      <c r="U93" s="3">
         <v>494</v>
       </c>
-      <c r="V93" s="5">
+      <c r="V93" s="3">
         <v>965</v>
       </c>
+      <c r="W93" s="1">
+        <f t="shared" si="1"/>
+        <v>60.001000366173685</v>
+      </c>
     </row>
-    <row r="94" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="J94" s="5">
+    <row r="94" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G94" s="2" t="b" cm="1">
+        <f t="array" ref="G94">AND(K94:N94=S94:V94)</f>
+        <v>1</v>
+      </c>
+      <c r="J94" s="3">
         <v>85</v>
       </c>
-      <c r="K94" s="5">
+      <c r="K94" s="3">
         <v>2172</v>
       </c>
-      <c r="L94" s="5">
+      <c r="L94" s="3">
         <v>2439</v>
       </c>
-      <c r="M94" s="5">
+      <c r="M94" s="3">
         <v>502</v>
       </c>
-      <c r="N94" s="5">
+      <c r="N94" s="3">
         <v>970</v>
       </c>
-      <c r="O94" s="5" t="s">
+      <c r="O94" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q94" s="5" t="s">
+      <c r="Q94" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="R94" s="5">
+      <c r="R94" s="3">
         <v>85</v>
       </c>
-      <c r="S94" s="5">
+      <c r="S94" s="3">
         <v>2172</v>
       </c>
-      <c r="T94" s="5">
+      <c r="T94" s="3">
         <v>2439</v>
       </c>
-      <c r="U94" s="5">
+      <c r="U94" s="3">
         <v>502</v>
       </c>
-      <c r="V94" s="5">
+      <c r="V94" s="3">
         <v>970</v>
       </c>
+      <c r="W94" s="1">
+        <f t="shared" si="1"/>
+        <v>59.999999566935003</v>
+      </c>
     </row>
-    <row r="95" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="J95" s="5">
+    <row r="95" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G95" s="2" t="b" cm="1">
+        <f t="array" ref="G95">AND(K95:N95=S95:V95)</f>
+        <v>1</v>
+      </c>
+      <c r="J95" s="3">
         <v>86</v>
       </c>
-      <c r="K95" s="5">
+      <c r="K95" s="3">
         <v>2179</v>
       </c>
-      <c r="L95" s="5">
+      <c r="L95" s="3">
         <v>2446</v>
       </c>
-      <c r="M95" s="5">
+      <c r="M95" s="3">
         <v>513</v>
       </c>
-      <c r="N95" s="5">
+      <c r="N95" s="3">
         <v>980</v>
       </c>
-      <c r="O95" s="5" t="s">
+      <c r="O95" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="Q95" s="5" t="s">
+      <c r="Q95" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="R95" s="5">
+      <c r="R95" s="3">
         <v>86</v>
       </c>
-      <c r="S95" s="5">
+      <c r="S95" s="3">
         <v>2179</v>
       </c>
-      <c r="T95" s="5">
+      <c r="T95" s="3">
         <v>2446</v>
       </c>
-      <c r="U95" s="5">
+      <c r="U95" s="3">
         <v>513</v>
       </c>
-      <c r="V95" s="5">
+      <c r="V95" s="3">
         <v>980</v>
       </c>
+      <c r="W95" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="96" spans="6:22" x14ac:dyDescent="0.25">
-      <c r="J96" s="5">
+    <row r="96" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G96" s="2" t="b" cm="1">
+        <f t="array" ref="G96">AND(K96:N96=S96:V96)</f>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3">
         <v>87</v>
       </c>
-      <c r="K96" s="5">
+      <c r="K96" s="3">
         <v>2182</v>
       </c>
-      <c r="L96" s="5">
+      <c r="L96" s="3">
         <v>2455</v>
       </c>
-      <c r="M96" s="5">
+      <c r="M96" s="3">
         <v>508</v>
       </c>
-      <c r="N96" s="5">
+      <c r="N96" s="3">
         <v>992</v>
       </c>
-      <c r="O96" s="5" t="s">
+      <c r="O96" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="Q96" s="5" t="s">
+      <c r="Q96" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="R96" s="5">
+      <c r="R96" s="3">
         <v>87</v>
       </c>
-      <c r="S96" s="5">
+      <c r="S96" s="3">
         <v>2182</v>
       </c>
-      <c r="T96" s="5">
+      <c r="T96" s="3">
         <v>2455</v>
       </c>
-      <c r="U96" s="5">
+      <c r="U96" s="3">
         <v>508</v>
       </c>
-      <c r="V96" s="5">
+      <c r="V96" s="3">
         <v>992</v>
       </c>
+      <c r="W96" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="97" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="J97" s="5">
+    <row r="97" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G97" s="2" t="b" cm="1">
+        <f t="array" ref="G97">AND(K97:N97=S97:V97)</f>
+        <v>1</v>
+      </c>
+      <c r="J97" s="3">
         <v>88</v>
       </c>
-      <c r="K97" s="5">
+      <c r="K97" s="3">
         <v>2184</v>
       </c>
-      <c r="L97" s="5">
+      <c r="L97" s="3">
         <v>2455</v>
       </c>
-      <c r="M97" s="5">
+      <c r="M97" s="3">
         <v>502</v>
       </c>
-      <c r="N97" s="5">
+      <c r="N97" s="3">
         <v>1000</v>
       </c>
-      <c r="O97" s="5" t="s">
+      <c r="O97" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="Q97" s="5" t="s">
+      <c r="Q97" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="R97" s="5">
+      <c r="R97" s="3">
         <v>88</v>
       </c>
-      <c r="S97" s="5">
+      <c r="S97" s="3">
         <v>2184</v>
       </c>
-      <c r="T97" s="5">
+      <c r="T97" s="3">
         <v>2455</v>
       </c>
-      <c r="U97" s="5">
+      <c r="U97" s="3">
         <v>502</v>
       </c>
-      <c r="V97" s="5">
+      <c r="V97" s="3">
         <v>1000</v>
       </c>
+      <c r="W97" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000999737530947</v>
+      </c>
     </row>
-    <row r="98" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="J98" s="5">
+    <row r="98" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G98" s="2" t="b" cm="1">
+        <f t="array" ref="G98">AND(K98:N98=S98:V98)</f>
+        <v>1</v>
+      </c>
+      <c r="J98" s="3">
         <v>89</v>
       </c>
-      <c r="K98" s="5">
+      <c r="K98" s="3">
         <v>2189</v>
       </c>
-      <c r="L98" s="5">
+      <c r="L98" s="3">
         <v>2460</v>
       </c>
-      <c r="M98" s="5">
+      <c r="M98" s="3">
         <v>514</v>
       </c>
-      <c r="N98" s="5">
+      <c r="N98" s="3">
         <v>1001</v>
       </c>
-      <c r="O98" s="5" t="s">
+      <c r="O98" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q98" s="5" t="s">
+      <c r="Q98" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="R98" s="5">
+      <c r="R98" s="3">
         <v>89</v>
       </c>
-      <c r="S98" s="5">
+      <c r="S98" s="3">
         <v>2189</v>
       </c>
-      <c r="T98" s="5">
+      <c r="T98" s="3">
         <v>2460</v>
       </c>
-      <c r="U98" s="5">
+      <c r="U98" s="3">
         <v>514</v>
       </c>
-      <c r="V98" s="5">
+      <c r="V98" s="3">
         <v>1001</v>
       </c>
+      <c r="W98" s="1">
+        <f t="shared" si="1"/>
+        <v>60.000000195577741</v>
+      </c>
     </row>
-    <row r="99" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="Q99" s="7" t="s">
+    <row r="99" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="Q99" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="R99" s="7"/>
-      <c r="S99" s="7"/>
-      <c r="T99" s="7"/>
+      <c r="R99" s="9"/>
+      <c r="S99" s="9"/>
+      <c r="T99" s="9"/>
     </row>
-    <row r="100" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="Q100" s="3">
+    <row r="100" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="Q100" s="8">
         <v>5340.15</v>
       </c>
-      <c r="R100" s="3"/>
-      <c r="S100" s="3"/>
-      <c r="T100" s="4" t="s">
+      <c r="R100" s="8"/>
+      <c r="S100" s="8"/>
+      <c r="T100" s="2" t="s">
         <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="AC77:AF77"/>
+    <mergeCell ref="Y76:AF76"/>
     <mergeCell ref="Q100:S100"/>
     <mergeCell ref="Q99:T99"/>
     <mergeCell ref="J7:O7"/>
     <mergeCell ref="Q7:V7"/>
     <mergeCell ref="Y77:AB77"/>
-    <mergeCell ref="AC77:AF77"/>
-    <mergeCell ref="Y76:AF76"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13435,12 +14909,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
